--- a/frontend/public/formats/physical_format.xlsx
+++ b/frontend/public/formats/physical_format.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PROJECTS FOLDER\SG ENCON\frontend\public\formats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF13FBBF-4047-499A-BAA3-D17BF968AA82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1204D4B9-74CD-4734-AB19-573AED4EBEFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="45">
   <si>
     <t>Cluster</t>
   </si>
@@ -182,9 +182,6 @@
   </si>
   <si>
     <t>ESIC IP No</t>
-  </si>
-  <si>
-    <t>Bhatinda</t>
   </si>
   <si>
     <t>Punjab SHQ</t>
@@ -2163,7 +2160,7 @@
         <v>24</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="C3"/>
       <c r="D3"/>
@@ -2459,7 +2456,7 @@
         <v>24</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C11"/>
       <c r="D11"/>

--- a/frontend/public/formats/physical_format.xlsx
+++ b/frontend/public/formats/physical_format.xlsx
@@ -1,23 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PROJECTS FOLDER\SG ENCON\frontend\public\formats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1204D4B9-74CD-4734-AB19-573AED4EBEFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DD974C0-3191-424D-84F6-CD6C52C5B90B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Employee Master" sheetId="85" r:id="rId1"/>
-    <sheet name="Attendance Status" sheetId="89" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Attendance Status'!$B$3:$B$12</definedName>
     <definedName name="Sheet19841630217081661">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -50,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="69">
   <si>
     <t>Cluster</t>
   </si>
@@ -127,18 +125,9 @@
     <t>Punjab</t>
   </si>
   <si>
-    <t>Pending</t>
-  </si>
-  <si>
-    <t>Received</t>
-  </si>
-  <si>
     <t>CMP</t>
   </si>
   <si>
-    <t>Daily Attendance Status</t>
-  </si>
-  <si>
     <t>Father Name</t>
   </si>
   <si>
@@ -185,18 +174,98 @@
   </si>
   <si>
     <t>Punjab SHQ</t>
+  </si>
+  <si>
+    <t>Delhi</t>
+  </si>
+  <si>
+    <t>Delhi SHQ</t>
+  </si>
+  <si>
+    <t>Delhi-1 (West)</t>
+  </si>
+  <si>
+    <t>Delhi-2 (South)</t>
+  </si>
+  <si>
+    <t>Delhi-3 (Central-East)</t>
+  </si>
+  <si>
+    <t>Delhi-4 (North)</t>
+  </si>
+  <si>
+    <t>Faridabad (NCR)</t>
+  </si>
+  <si>
+    <t>Ghaziabad (NCR)</t>
+  </si>
+  <si>
+    <t>Gurgaon (NCR)</t>
+  </si>
+  <si>
+    <t>Noida (NCR)</t>
+  </si>
+  <si>
+    <t>Haryana</t>
+  </si>
+  <si>
+    <t>Haryana SHQ</t>
+  </si>
+  <si>
+    <t>Ambala</t>
+  </si>
+  <si>
+    <t>Hissar</t>
+  </si>
+  <si>
+    <t>Karnal</t>
+  </si>
+  <si>
+    <t>Panipat</t>
+  </si>
+  <si>
+    <t>Palwal</t>
+  </si>
+  <si>
+    <t>Rewari</t>
+  </si>
+  <si>
+    <t>Rohtak</t>
+  </si>
+  <si>
+    <t>UP East</t>
+  </si>
+  <si>
+    <t>UP East SHQ</t>
+  </si>
+  <si>
+    <t>Allahabad</t>
+  </si>
+  <si>
+    <t>Azamgarh</t>
+  </si>
+  <si>
+    <t>Faizabad</t>
+  </si>
+  <si>
+    <t>Gorakhpur</t>
+  </si>
+  <si>
+    <t>Raibareilly</t>
+  </si>
+  <si>
+    <t>Varanasi</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="44" formatCode="_ &quot;₹&quot;\ * #,##0.00_ ;_ &quot;₹&quot;\ * \-#,##0.00_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="164" formatCode="[$-14009]dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="83">
+  <fonts count="84">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -759,16 +828,21 @@
       <family val="1"/>
     </font>
     <font>
-      <b/>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
@@ -952,7 +1026,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -1083,56 +1157,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
         <color indexed="64"/>
       </right>
       <top/>
@@ -1141,77 +1169,8 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="204">
+  <cellStyleXfs count="205">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0"/>
@@ -1416,68 +1375,25 @@
     <xf numFmtId="0" fontId="73" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="82" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="180" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="204" applyFont="1"/>
+    <xf numFmtId="9" fontId="74" fillId="0" borderId="0" xfId="204" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="74" fillId="0" borderId="0" xfId="204" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="74" fillId="0" borderId="0" xfId="180" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="204" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="83" fillId="0" borderId="1" xfId="204" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="74" fillId="0" borderId="0" xfId="180" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="74" fillId="0" borderId="0" xfId="180" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="81" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="81" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="81" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="204" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="11" xfId="204" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="204">
+  <cellStyles count="205">
     <cellStyle name="20% - Accent1" xfId="41" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent1 2" xfId="101" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="20% - Accent1 3" xfId="138" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
@@ -1669,6 +1585,7 @@
     <cellStyle name="Note 2 2" xfId="114" xr:uid="{00000000-0005-0000-0000-0000A0000000}"/>
     <cellStyle name="Note 3" xfId="137" xr:uid="{00000000-0005-0000-0000-0000A1000000}"/>
     <cellStyle name="Output" xfId="33" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Percent" xfId="204" builtinId="5"/>
     <cellStyle name="Percent 2" xfId="70" xr:uid="{00000000-0005-0000-0000-0000A4000000}"/>
     <cellStyle name="Percent 3" xfId="80" xr:uid="{00000000-0005-0000-0000-0000A5000000}"/>
     <cellStyle name="Percent 3 2" xfId="129" xr:uid="{00000000-0005-0000-0000-0000A6000000}"/>
@@ -1683,28 +1600,7 @@
     <cellStyle name="Total" xfId="39" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="37" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
   <colors>
     <mruColors>
@@ -2011,644 +1907,741 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{669DF689-B0D6-46EA-ACFD-66E425F22CA2}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AF11"/>
+  <dimension ref="A1:AF38"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="16" width="8.77734375" style="1"/>
-    <col min="17" max="17" width="8.77734375" style="2"/>
-    <col min="18" max="18" width="8.77734375" style="1"/>
-    <col min="19" max="20" width="8.77734375" style="3"/>
-    <col min="21" max="27" width="8.77734375" style="1"/>
-    <col min="28" max="32" width="8.77734375" style="4"/>
-    <col min="33" max="16384" width="8.77734375" style="1"/>
+    <col min="1" max="1" width="7.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.21875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.21875" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4" style="3" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="8.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="7.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="7.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="9.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="8.77734375" style="2"/>
+    <col min="33" max="16384" width="8.77734375" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31">
-      <c r="A1" t="s">
+      <c r="A1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="O1" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="P1" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" t="s">
+      <c r="Q1" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="J1" t="s">
-        <v>3</v>
-      </c>
-      <c r="K1" t="s">
-        <v>32</v>
-      </c>
-      <c r="L1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M1" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" t="s">
+      <c r="R1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="S1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="T1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="U1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="V1" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="O1" t="s">
-        <v>30</v>
-      </c>
-      <c r="P1" t="s">
+      <c r="W1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="X1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z1" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="R1" t="s">
-        <v>13</v>
-      </c>
-      <c r="S1" t="s">
-        <v>2</v>
-      </c>
-      <c r="T1" t="s">
-        <v>11</v>
-      </c>
-      <c r="U1" t="s">
-        <v>10</v>
-      </c>
-      <c r="V1" t="s">
+      <c r="AA1" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="W1" t="s">
+      <c r="AB1" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="X1" t="s">
-        <v>7</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>31</v>
-      </c>
-      <c r="Z1" t="s">
+      <c r="AC1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD1" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AE1" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31">
+      <c r="A2" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+      <c r="Y2" s="1"/>
+      <c r="Z2" s="1"/>
+      <c r="AA2" s="1"/>
+      <c r="AB2" s="1"/>
+      <c r="AC2" s="1"/>
+      <c r="AD2" s="1"/>
+      <c r="AE2" s="1"/>
+    </row>
+    <row r="3" spans="1:31">
+      <c r="A3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+      <c r="R3" s="1"/>
+      <c r="S3" s="1"/>
+      <c r="T3" s="1"/>
+      <c r="U3" s="1"/>
+      <c r="V3" s="1"/>
+      <c r="W3" s="1"/>
+      <c r="X3" s="1"/>
+      <c r="Y3" s="1"/>
+      <c r="Z3" s="1"/>
+      <c r="AA3" s="1"/>
+      <c r="AB3" s="1"/>
+      <c r="AC3" s="1"/>
+      <c r="AD3" s="1"/>
+      <c r="AE3" s="1"/>
+    </row>
+    <row r="4" spans="1:31">
+      <c r="A4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="1"/>
+      <c r="S4" s="1"/>
+      <c r="T4" s="1"/>
+      <c r="U4" s="1"/>
+      <c r="V4" s="1"/>
+      <c r="W4" s="1"/>
+      <c r="X4" s="1"/>
+      <c r="Y4" s="1"/>
+      <c r="Z4" s="1"/>
+      <c r="AA4" s="1"/>
+      <c r="AB4" s="1"/>
+      <c r="AC4" s="1"/>
+      <c r="AD4" s="1"/>
+      <c r="AE4" s="1"/>
+    </row>
+    <row r="5" spans="1:31">
+      <c r="A5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
+      <c r="R5" s="1"/>
+      <c r="S5" s="1"/>
+      <c r="T5" s="1"/>
+      <c r="U5" s="1"/>
+      <c r="V5" s="1"/>
+      <c r="W5" s="1"/>
+      <c r="X5" s="1"/>
+      <c r="Y5" s="1"/>
+      <c r="Z5" s="1"/>
+      <c r="AA5" s="1"/>
+      <c r="AB5" s="1"/>
+      <c r="AC5" s="1"/>
+      <c r="AD5" s="1"/>
+      <c r="AE5" s="1"/>
+    </row>
+    <row r="6" spans="1:31">
+      <c r="A6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+      <c r="T6" s="1"/>
+      <c r="U6" s="1"/>
+      <c r="V6" s="1"/>
+      <c r="W6" s="1"/>
+      <c r="X6" s="1"/>
+      <c r="Y6" s="1"/>
+      <c r="Z6" s="1"/>
+      <c r="AA6" s="1"/>
+      <c r="AB6" s="1"/>
+      <c r="AC6" s="1"/>
+      <c r="AD6" s="1"/>
+      <c r="AE6" s="1"/>
+    </row>
+    <row r="7" spans="1:31">
+      <c r="A7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="1"/>
+      <c r="S7" s="1"/>
+      <c r="T7" s="1"/>
+      <c r="U7" s="1"/>
+      <c r="V7" s="1"/>
+      <c r="W7" s="1"/>
+      <c r="X7" s="1"/>
+      <c r="Y7" s="1"/>
+      <c r="Z7" s="1"/>
+      <c r="AA7" s="1"/>
+      <c r="AB7" s="1"/>
+      <c r="AC7" s="1"/>
+      <c r="AD7" s="1"/>
+      <c r="AE7" s="1"/>
+    </row>
+    <row r="8" spans="1:31">
+      <c r="A8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1"/>
+      <c r="S8" s="1"/>
+      <c r="T8" s="1"/>
+      <c r="U8" s="1"/>
+      <c r="V8" s="1"/>
+      <c r="W8" s="1"/>
+      <c r="X8" s="1"/>
+      <c r="Y8" s="1"/>
+      <c r="Z8" s="1"/>
+      <c r="AA8" s="1"/>
+      <c r="AB8" s="1"/>
+      <c r="AC8" s="1"/>
+      <c r="AD8" s="1"/>
+      <c r="AE8" s="1"/>
+    </row>
+    <row r="9" spans="1:31">
+      <c r="A9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+      <c r="T9" s="1"/>
+      <c r="U9" s="1"/>
+      <c r="V9" s="1"/>
+      <c r="W9" s="1"/>
+      <c r="X9" s="1"/>
+      <c r="Y9" s="1"/>
+      <c r="Z9" s="1"/>
+      <c r="AA9" s="1"/>
+      <c r="AB9" s="1"/>
+      <c r="AC9" s="1"/>
+      <c r="AD9" s="1"/>
+      <c r="AE9" s="1"/>
+    </row>
+    <row r="10" spans="1:31">
+      <c r="A10" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1"/>
+      <c r="Q10" s="1"/>
+      <c r="R10" s="1"/>
+      <c r="S10" s="1"/>
+      <c r="T10" s="1"/>
+      <c r="U10" s="1"/>
+      <c r="V10" s="1"/>
+      <c r="W10" s="1"/>
+      <c r="X10" s="1"/>
+      <c r="Y10" s="1"/>
+      <c r="Z10" s="1"/>
+      <c r="AA10" s="1"/>
+      <c r="AB10" s="1"/>
+      <c r="AC10" s="1"/>
+      <c r="AD10" s="1"/>
+      <c r="AE10" s="1"/>
+    </row>
+    <row r="11" spans="1:31">
+      <c r="A11" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+      <c r="U11" s="1"/>
+      <c r="V11" s="1"/>
+      <c r="W11" s="1"/>
+      <c r="X11" s="1"/>
+      <c r="Y11" s="1"/>
+      <c r="Z11" s="1"/>
+      <c r="AA11" s="1"/>
+      <c r="AB11" s="1"/>
+      <c r="AC11" s="1"/>
+      <c r="AD11" s="1"/>
+      <c r="AE11" s="1"/>
+    </row>
+    <row r="12" spans="1:31">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1"/>
+      <c r="R12" s="1"/>
+      <c r="S12" s="1"/>
+      <c r="T12" s="1"/>
+      <c r="U12" s="1"/>
+      <c r="V12" s="1"/>
+      <c r="W12" s="1"/>
+      <c r="X12" s="1"/>
+      <c r="Y12" s="1"/>
+      <c r="Z12" s="1"/>
+      <c r="AA12" s="1"/>
+      <c r="AB12" s="1"/>
+      <c r="AC12" s="1"/>
+      <c r="AD12" s="1"/>
+      <c r="AE12" s="1"/>
+    </row>
+    <row r="13" spans="1:31">
+      <c r="A13" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="AC1" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD1" t="s">
+      <c r="B13" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="AE1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:31">
-      <c r="A2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2"/>
-      <c r="D2"/>
-      <c r="E2"/>
-      <c r="F2"/>
-      <c r="G2"/>
-      <c r="H2"/>
-      <c r="I2"/>
-      <c r="J2"/>
-      <c r="K2"/>
-      <c r="L2"/>
-      <c r="M2"/>
-      <c r="N2"/>
-      <c r="O2"/>
-      <c r="P2"/>
-      <c r="Q2"/>
-      <c r="R2"/>
-      <c r="S2"/>
-      <c r="T2"/>
-      <c r="U2"/>
-      <c r="V2"/>
-      <c r="W2"/>
-      <c r="X2"/>
-      <c r="Y2"/>
-      <c r="Z2"/>
-      <c r="AA2"/>
-      <c r="AB2"/>
-      <c r="AC2"/>
-      <c r="AD2"/>
-      <c r="AE2"/>
-    </row>
-    <row r="3" spans="1:31">
-      <c r="A3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3"/>
-      <c r="D3"/>
-      <c r="E3"/>
-      <c r="F3"/>
-      <c r="G3"/>
-      <c r="H3"/>
-      <c r="I3"/>
-      <c r="J3"/>
-      <c r="K3"/>
-      <c r="L3"/>
-      <c r="M3"/>
-      <c r="N3"/>
-      <c r="O3"/>
-      <c r="P3"/>
-      <c r="Q3"/>
-      <c r="R3"/>
-      <c r="S3"/>
-      <c r="T3"/>
-      <c r="U3"/>
-      <c r="V3"/>
-      <c r="W3"/>
-      <c r="X3"/>
-      <c r="Y3"/>
-      <c r="Z3"/>
-      <c r="AA3"/>
-      <c r="AB3"/>
-      <c r="AC3"/>
-      <c r="AD3"/>
-      <c r="AE3"/>
-    </row>
-    <row r="4" spans="1:31">
-      <c r="A4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4"/>
-      <c r="D4"/>
-      <c r="E4"/>
-      <c r="F4"/>
-      <c r="G4"/>
-      <c r="H4"/>
-      <c r="I4"/>
-      <c r="J4"/>
-      <c r="K4"/>
-      <c r="L4"/>
-      <c r="M4"/>
-      <c r="N4"/>
-      <c r="O4"/>
-      <c r="P4"/>
-      <c r="Q4"/>
-      <c r="R4"/>
-      <c r="S4"/>
-      <c r="T4"/>
-      <c r="U4"/>
-      <c r="V4"/>
-      <c r="W4"/>
-      <c r="X4"/>
-      <c r="Y4"/>
-      <c r="Z4"/>
-      <c r="AA4"/>
-      <c r="AB4"/>
-      <c r="AC4"/>
-      <c r="AD4"/>
-      <c r="AE4"/>
-    </row>
-    <row r="5" spans="1:31">
-      <c r="A5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5"/>
-      <c r="D5"/>
-      <c r="E5"/>
-      <c r="F5"/>
-      <c r="G5"/>
-      <c r="H5"/>
-      <c r="I5"/>
-      <c r="J5"/>
-      <c r="K5"/>
-      <c r="L5"/>
-      <c r="M5"/>
-      <c r="N5"/>
-      <c r="O5"/>
-      <c r="P5"/>
-      <c r="Q5"/>
-      <c r="R5"/>
-      <c r="S5"/>
-      <c r="T5"/>
-      <c r="U5"/>
-      <c r="V5"/>
-      <c r="W5"/>
-      <c r="X5"/>
-      <c r="Y5"/>
-      <c r="Z5"/>
-      <c r="AA5"/>
-      <c r="AB5"/>
-      <c r="AC5"/>
-      <c r="AD5"/>
-      <c r="AE5"/>
-    </row>
-    <row r="6" spans="1:31">
-      <c r="A6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6"/>
-      <c r="D6"/>
-      <c r="E6"/>
-      <c r="F6"/>
-      <c r="G6"/>
-      <c r="H6"/>
-      <c r="I6"/>
-      <c r="J6"/>
-      <c r="K6"/>
-      <c r="L6"/>
-      <c r="M6"/>
-      <c r="N6"/>
-      <c r="O6"/>
-      <c r="P6"/>
-      <c r="Q6"/>
-      <c r="R6"/>
-      <c r="S6"/>
-      <c r="T6"/>
-      <c r="U6"/>
-      <c r="V6"/>
-      <c r="W6"/>
-      <c r="X6"/>
-      <c r="Y6"/>
-      <c r="Z6"/>
-      <c r="AA6"/>
-      <c r="AB6"/>
-      <c r="AC6"/>
-      <c r="AD6"/>
-      <c r="AE6"/>
-    </row>
-    <row r="7" spans="1:31">
-      <c r="A7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7"/>
-      <c r="D7"/>
-      <c r="E7"/>
-      <c r="F7"/>
-      <c r="G7"/>
-      <c r="H7"/>
-      <c r="I7"/>
-      <c r="J7"/>
-      <c r="K7"/>
-      <c r="L7"/>
-      <c r="M7"/>
-      <c r="N7"/>
-      <c r="O7"/>
-      <c r="P7"/>
-      <c r="Q7"/>
-      <c r="R7"/>
-      <c r="S7"/>
-      <c r="T7"/>
-      <c r="U7"/>
-      <c r="V7"/>
-      <c r="W7"/>
-      <c r="X7"/>
-      <c r="Y7"/>
-      <c r="Z7"/>
-      <c r="AA7"/>
-      <c r="AB7"/>
-      <c r="AC7"/>
-      <c r="AD7"/>
-      <c r="AE7"/>
-    </row>
-    <row r="8" spans="1:31">
-      <c r="A8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8"/>
-      <c r="D8"/>
-      <c r="E8"/>
-      <c r="F8"/>
-      <c r="G8"/>
-      <c r="H8"/>
-      <c r="I8"/>
-      <c r="J8"/>
-      <c r="K8"/>
-      <c r="L8"/>
-      <c r="M8"/>
-      <c r="N8"/>
-      <c r="O8"/>
-      <c r="P8"/>
-      <c r="Q8"/>
-      <c r="R8"/>
-      <c r="S8"/>
-      <c r="T8"/>
-      <c r="U8"/>
-      <c r="V8"/>
-      <c r="W8"/>
-      <c r="X8"/>
-      <c r="Y8"/>
-      <c r="Z8"/>
-      <c r="AA8"/>
-      <c r="AB8"/>
-      <c r="AC8"/>
-      <c r="AD8"/>
-      <c r="AE8"/>
-    </row>
-    <row r="9" spans="1:31">
-      <c r="A9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9"/>
-      <c r="D9"/>
-      <c r="E9"/>
-      <c r="F9"/>
-      <c r="G9"/>
-      <c r="H9"/>
-      <c r="I9"/>
-      <c r="J9"/>
-      <c r="K9"/>
-      <c r="L9"/>
-      <c r="M9"/>
-      <c r="N9"/>
-      <c r="O9"/>
-      <c r="P9"/>
-      <c r="Q9"/>
-      <c r="R9"/>
-      <c r="S9"/>
-      <c r="T9"/>
-      <c r="U9"/>
-      <c r="V9"/>
-      <c r="W9"/>
-      <c r="X9"/>
-      <c r="Y9"/>
-      <c r="Z9"/>
-      <c r="AA9"/>
-      <c r="AB9"/>
-      <c r="AC9"/>
-      <c r="AD9"/>
-      <c r="AE9"/>
-    </row>
-    <row r="10" spans="1:31">
-      <c r="A10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10"/>
-      <c r="D10"/>
-      <c r="E10"/>
-      <c r="F10"/>
-      <c r="G10"/>
-      <c r="H10"/>
-      <c r="I10"/>
-      <c r="J10"/>
-      <c r="K10"/>
-      <c r="L10"/>
-      <c r="M10"/>
-      <c r="N10"/>
-      <c r="O10"/>
-      <c r="P10"/>
-      <c r="Q10"/>
-      <c r="R10"/>
-      <c r="S10"/>
-      <c r="T10"/>
-      <c r="U10"/>
-      <c r="V10"/>
-      <c r="W10"/>
-      <c r="X10"/>
-      <c r="Y10"/>
-      <c r="Z10"/>
-      <c r="AA10"/>
-      <c r="AB10"/>
-      <c r="AC10"/>
-      <c r="AD10"/>
-      <c r="AE10"/>
-    </row>
-    <row r="11" spans="1:31">
-      <c r="A11" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" t="s">
+    </row>
+    <row r="14" spans="1:31">
+      <c r="A14" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C11"/>
-      <c r="D11"/>
-      <c r="E11"/>
-      <c r="F11"/>
-      <c r="G11"/>
-      <c r="H11"/>
-      <c r="I11"/>
-      <c r="J11"/>
-      <c r="K11"/>
-      <c r="L11"/>
-      <c r="M11"/>
-      <c r="N11"/>
-      <c r="O11"/>
-      <c r="P11"/>
-      <c r="Q11"/>
-      <c r="R11"/>
-      <c r="S11"/>
-      <c r="T11"/>
-      <c r="U11"/>
-      <c r="V11"/>
-      <c r="W11"/>
-      <c r="X11"/>
-      <c r="Y11"/>
-      <c r="Z11"/>
-      <c r="AA11"/>
-      <c r="AB11"/>
-      <c r="AC11"/>
-      <c r="AD11"/>
-      <c r="AE11"/>
+    </row>
+    <row r="15" spans="1:31">
+      <c r="A15" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31">
+      <c r="A16" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="6"/>
+      <c r="B31" s="6"/>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>68</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="82" type="noConversion"/>
+  <phoneticPr fontId="81" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C8A80A6-0B7D-448A-ABEA-B114B4AD3029}">
-  <sheetPr codeName="Sheet6"/>
-  <dimension ref="B2:H12"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="2.6640625" style="6" customWidth="1"/>
-    <col min="2" max="2" width="13.77734375" style="6" customWidth="1"/>
-    <col min="3" max="3" width="8.21875" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.77734375" style="6"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:8" ht="15" thickBot="1">
-      <c r="B2" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-    </row>
-    <row r="3" spans="2:8" ht="15" thickBot="1">
-      <c r="B3" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" s="10">
-        <v>46143</v>
-      </c>
-      <c r="D3" s="8">
-        <f>C3+1</f>
-        <v>46144</v>
-      </c>
-      <c r="E3" s="5">
-        <f>D3+1</f>
-        <v>46145</v>
-      </c>
-      <c r="F3" s="5">
-        <f>E3+1</f>
-        <v>46146</v>
-      </c>
-    </row>
-    <row r="4" spans="2:8">
-      <c r="B4" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-    </row>
-    <row r="5" spans="2:8">
-      <c r="B5" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="9"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-    </row>
-    <row r="6" spans="2:8">
-      <c r="B6" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="9"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-    </row>
-    <row r="7" spans="2:8">
-      <c r="B7" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-    </row>
-    <row r="8" spans="2:8">
-      <c r="B8" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="9"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-    </row>
-    <row r="9" spans="2:8">
-      <c r="B9" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="9"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-    </row>
-    <row r="10" spans="2:8">
-      <c r="B10" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-    </row>
-    <row r="11" spans="2:8">
-      <c r="B11" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-    </row>
-    <row r="12" spans="2:8" ht="15" thickBot="1">
-      <c r="B12" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2:H2"/>
-  </mergeCells>
-  <conditionalFormatting sqref="C4:F12">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
-      <formula>"Received"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
-      <formula>"Pending"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/frontend/public/formats/physical_format.xlsx
+++ b/frontend/public/formats/physical_format.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PROJECTS FOLDER\SG ENCON\frontend\public\formats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DD974C0-3191-424D-84F6-CD6C52C5B90B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74712765-1DF3-46C8-971B-1B7FDF108127}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="76">
   <si>
     <t>Cluster</t>
   </si>
@@ -255,6 +255,27 @@
   </si>
   <si>
     <t>Varanasi</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>Inactive</t>
+  </si>
+  <si>
+    <t>Pending</t>
+  </si>
+  <si>
+    <t>Not Applicable</t>
+  </si>
+  <si>
+    <t>Company</t>
+  </si>
+  <si>
+    <t>Own</t>
+  </si>
+  <si>
+    <t>Not Required</t>
   </si>
 </sst>
 </file>
@@ -2047,7 +2068,9 @@
       <c r="B2" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="1"/>
+      <c r="C2" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
@@ -2062,13 +2085,17 @@
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
-      <c r="R2" s="1"/>
+      <c r="R2" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="S2" s="1"/>
       <c r="T2" s="1"/>
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
       <c r="W2" s="1"/>
-      <c r="X2" s="1"/>
+      <c r="X2" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
       <c r="AA2" s="1"/>
@@ -2084,7 +2111,9 @@
       <c r="B3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="1"/>
+      <c r="C3" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -2099,13 +2128,17 @@
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
-      <c r="R3" s="1"/>
+      <c r="R3" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="S3" s="1"/>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
       <c r="W3" s="1"/>
-      <c r="X3" s="1"/>
+      <c r="X3" s="1" t="s">
+        <v>74</v>
+      </c>
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
       <c r="AA3" s="1"/>
@@ -2121,7 +2154,9 @@
       <c r="B4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="1"/>
+      <c r="C4" s="1" t="s">
+        <v>71</v>
+      </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
@@ -2142,7 +2177,9 @@
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
       <c r="W4" s="1"/>
-      <c r="X4" s="1"/>
+      <c r="X4" s="1" t="s">
+        <v>75</v>
+      </c>
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
       <c r="AA4" s="1"/>
@@ -2158,7 +2195,9 @@
       <c r="B5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="1"/>
+      <c r="C5" s="1" t="s">
+        <v>72</v>
+      </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>

--- a/frontend/public/formats/physical_format.xlsx
+++ b/frontend/public/formats/physical_format.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PROJECTS FOLDER\SG ENCON\frontend\public\formats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74712765-1DF3-46C8-971B-1B7FDF108127}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{996B7389-E052-48DD-9A82-4E179DD57ED0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="127">
   <si>
     <t>Cluster</t>
   </si>
@@ -276,6 +276,159 @@
   </si>
   <si>
     <t>Not Required</t>
+  </si>
+  <si>
+    <t>Admin Head</t>
+  </si>
+  <si>
+    <t>Analyst-Fiber</t>
+  </si>
+  <si>
+    <t>Analyst-Fttx</t>
+  </si>
+  <si>
+    <t>Analyst-IPCOLO</t>
+  </si>
+  <si>
+    <t>Analyst-ISP</t>
+  </si>
+  <si>
+    <t>Analyst-Material</t>
+  </si>
+  <si>
+    <t>Analyst-Planning</t>
+  </si>
+  <si>
+    <t>Analyst-PMO</t>
+  </si>
+  <si>
+    <t>Analyst-Power &amp; Fuel</t>
+  </si>
+  <si>
+    <t>Analyst-Utility</t>
+  </si>
+  <si>
+    <t>Assistant Splicer</t>
+  </si>
+  <si>
+    <t>CMP LEAD</t>
+  </si>
+  <si>
+    <t>Commercial Executive</t>
+  </si>
+  <si>
+    <t>Commercial Lead</t>
+  </si>
+  <si>
+    <t>Energy Lead</t>
+  </si>
+  <si>
+    <t>Estate Executive</t>
+  </si>
+  <si>
+    <t>Fiber SME</t>
+  </si>
+  <si>
+    <t>Fibre Supervisor</t>
+  </si>
+  <si>
+    <t>FRT Helper</t>
+  </si>
+  <si>
+    <t>Fttx Assistant Splicer</t>
+  </si>
+  <si>
+    <t>Fttx Engineer</t>
+  </si>
+  <si>
+    <t>Fttx Helper</t>
+  </si>
+  <si>
+    <t>Fttx Lead</t>
+  </si>
+  <si>
+    <t>Fttx Splicer</t>
+  </si>
+  <si>
+    <t>Fttx Supervisor</t>
+  </si>
+  <si>
+    <t>Fttx Technician</t>
+  </si>
+  <si>
+    <t>HR Executive</t>
+  </si>
+  <si>
+    <t>ISP Engineer</t>
+  </si>
+  <si>
+    <t>Legal Executive</t>
+  </si>
+  <si>
+    <t>MIS Executive</t>
+  </si>
+  <si>
+    <t>Office Helper</t>
+  </si>
+  <si>
+    <t>OMCR Lead</t>
+  </si>
+  <si>
+    <t>OMCR Resources</t>
+  </si>
+  <si>
+    <t>Other Roles - Temporary Technician</t>
+  </si>
+  <si>
+    <t>Patroller</t>
+  </si>
+  <si>
+    <t>Project Technician</t>
+  </si>
+  <si>
+    <t>Rigger</t>
+  </si>
+  <si>
+    <t>Route Guard</t>
+  </si>
+  <si>
+    <t>Splicer</t>
+  </si>
+  <si>
+    <t>State Fiber SME</t>
+  </si>
+  <si>
+    <t>State HR Head</t>
+  </si>
+  <si>
+    <t>State HSEF Officer</t>
+  </si>
+  <si>
+    <t>State ISP SME</t>
+  </si>
+  <si>
+    <t>State Material Manager</t>
+  </si>
+  <si>
+    <t>State Operation Head</t>
+  </si>
+  <si>
+    <t>State Utility SME</t>
+  </si>
+  <si>
+    <t>Technician</t>
+  </si>
+  <si>
+    <t>Utility Helper</t>
+  </si>
+  <si>
+    <t>Utility Supervisor</t>
+  </si>
+  <si>
+    <t>Warehouse Helper</t>
+  </si>
+  <si>
+    <t>Warehouse Incharge Cum Security</t>
   </si>
 </sst>
 </file>
@@ -286,7 +439,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;₹&quot;\ * #,##0.00_ ;_ &quot;₹&quot;\ * \-#,##0.00_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="84">
+  <fonts count="86">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -865,8 +1018,20 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0A3069"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F2328"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1044,6 +1209,48 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1398,7 +1605,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="82" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="204" applyFont="1"/>
     <xf numFmtId="9" fontId="74" fillId="0" borderId="0" xfId="204" applyFont="1" applyAlignment="1">
@@ -1407,12 +1614,28 @@
     <xf numFmtId="9" fontId="74" fillId="0" borderId="0" xfId="204" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="204" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="83" fillId="0" borderId="1" xfId="204" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="204" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="33" borderId="1" xfId="204" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="33" borderId="1" xfId="204" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="34" borderId="11" xfId="204" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="35" borderId="0" xfId="204" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="84" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="37" borderId="0" xfId="204" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="36" borderId="0" xfId="204" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="34" borderId="1" xfId="204" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="85" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="38" borderId="1" xfId="204" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="83" fillId="38" borderId="1" xfId="204" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="204" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="11" xfId="204" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="35" borderId="1" xfId="204" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="39" borderId="1" xfId="204" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="205">
     <cellStyle name="20% - Accent1" xfId="41" builtinId="30" customBuiltin="1"/>
@@ -1928,19 +2151,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{669DF689-B0D6-46EA-ACFD-66E425F22CA2}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AF38"/>
+  <dimension ref="A1:AF52"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="7.77734375" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.21875" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.88671875" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.44140625" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.77734375" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.44140625" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.5546875" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="8" style="3" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="23.21875" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="35.6640625" style="3" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="21.88671875" style="3" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.44140625" style="3" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="6.6640625" style="3" bestFit="1" customWidth="1"/>
@@ -1966,109 +2189,110 @@
     <col min="33" max="16384" width="8.77734375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:32">
+      <c r="A1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="O1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="P1" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="Q1" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="R1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="S1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="T1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="U1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="V1" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="W1" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="X1" s="4" t="s">
+      <c r="X1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="Y1" s="4" t="s">
+      <c r="Y1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="Z1" s="4" t="s">
+      <c r="Z1" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="AA1" s="4" t="s">
+      <c r="AA1" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="AB1" s="4" t="s">
+      <c r="AB1" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="AC1" s="4" t="s">
+      <c r="AC1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="AD1" s="4" t="s">
+      <c r="AD1" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="AE1" s="4" t="s">
+      <c r="AE1" s="5" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:31">
+      <c r="AF1" s="3"/>
+    </row>
+    <row r="2" spans="1:32">
       <c r="A2" s="7" t="s">
         <v>24</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="8" t="s">
         <v>69</v>
       </c>
       <c r="D2" s="1"/>
@@ -2077,7 +2301,9 @@
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
+      <c r="J2" s="9" t="s">
+        <v>76</v>
+      </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
@@ -2085,7 +2311,7 @@
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
-      <c r="R2" s="1" t="s">
+      <c r="R2" s="10" t="s">
         <v>69</v>
       </c>
       <c r="S2" s="1"/>
@@ -2093,7 +2319,7 @@
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
       <c r="W2" s="1"/>
-      <c r="X2" s="1" t="s">
+      <c r="X2" s="11" t="s">
         <v>73</v>
       </c>
       <c r="Y2" s="1"/>
@@ -2103,15 +2329,16 @@
       <c r="AC2" s="1"/>
       <c r="AD2" s="1"/>
       <c r="AE2" s="1"/>
-    </row>
-    <row r="3" spans="1:31">
-      <c r="A3" s="4" t="s">
+      <c r="AF2" s="3"/>
+    </row>
+    <row r="3" spans="1:32">
+      <c r="A3" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="8" t="s">
         <v>70</v>
       </c>
       <c r="D3" s="1"/>
@@ -2120,7 +2347,9 @@
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
+      <c r="J3" s="13" t="s">
+        <v>77</v>
+      </c>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
@@ -2128,7 +2357,7 @@
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
-      <c r="R3" s="1" t="s">
+      <c r="R3" s="10" t="s">
         <v>70</v>
       </c>
       <c r="S3" s="1"/>
@@ -2136,7 +2365,7 @@
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
       <c r="W3" s="1"/>
-      <c r="X3" s="1" t="s">
+      <c r="X3" s="11" t="s">
         <v>74</v>
       </c>
       <c r="Y3" s="1"/>
@@ -2146,15 +2375,16 @@
       <c r="AC3" s="1"/>
       <c r="AD3" s="1"/>
       <c r="AE3" s="1"/>
-    </row>
-    <row r="4" spans="1:31">
-      <c r="A4" s="4" t="s">
+      <c r="AF3" s="3"/>
+    </row>
+    <row r="4" spans="1:32">
+      <c r="A4" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="8" t="s">
         <v>71</v>
       </c>
       <c r="D4" s="1"/>
@@ -2163,7 +2393,9 @@
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
+      <c r="J4" s="13" t="s">
+        <v>78</v>
+      </c>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
@@ -2177,7 +2409,7 @@
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
       <c r="W4" s="1"/>
-      <c r="X4" s="1" t="s">
+      <c r="X4" s="11" t="s">
         <v>75</v>
       </c>
       <c r="Y4" s="1"/>
@@ -2187,15 +2419,16 @@
       <c r="AC4" s="1"/>
       <c r="AD4" s="1"/>
       <c r="AE4" s="1"/>
-    </row>
-    <row r="5" spans="1:31">
-      <c r="A5" s="4" t="s">
+      <c r="AF4" s="3"/>
+    </row>
+    <row r="5" spans="1:32">
+      <c r="A5" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="8" t="s">
         <v>72</v>
       </c>
       <c r="D5" s="1"/>
@@ -2204,7 +2437,9 @@
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
+      <c r="J5" s="13" t="s">
+        <v>79</v>
+      </c>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
@@ -2226,12 +2461,13 @@
       <c r="AC5" s="1"/>
       <c r="AD5" s="1"/>
       <c r="AE5" s="1"/>
-    </row>
-    <row r="6" spans="1:31">
-      <c r="A6" s="4" t="s">
+      <c r="AF5" s="3"/>
+    </row>
+    <row r="6" spans="1:32">
+      <c r="A6" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="12" t="s">
         <v>18</v>
       </c>
       <c r="C6" s="1"/>
@@ -2241,7 +2477,9 @@
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
+      <c r="J6" s="13" t="s">
+        <v>80</v>
+      </c>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -2263,12 +2501,13 @@
       <c r="AC6" s="1"/>
       <c r="AD6" s="1"/>
       <c r="AE6" s="1"/>
-    </row>
-    <row r="7" spans="1:31">
-      <c r="A7" s="4" t="s">
+      <c r="AF6" s="3"/>
+    </row>
+    <row r="7" spans="1:32">
+      <c r="A7" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="12" t="s">
         <v>19</v>
       </c>
       <c r="C7" s="1"/>
@@ -2278,7 +2517,9 @@
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
+      <c r="J7" s="13" t="s">
+        <v>81</v>
+      </c>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
@@ -2300,12 +2541,13 @@
       <c r="AC7" s="1"/>
       <c r="AD7" s="1"/>
       <c r="AE7" s="1"/>
-    </row>
-    <row r="8" spans="1:31">
-      <c r="A8" s="4" t="s">
+      <c r="AF7" s="3"/>
+    </row>
+    <row r="8" spans="1:32">
+      <c r="A8" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="12" t="s">
         <v>20</v>
       </c>
       <c r="C8" s="1"/>
@@ -2315,7 +2557,9 @@
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
+      <c r="J8" s="13" t="s">
+        <v>82</v>
+      </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -2337,12 +2581,13 @@
       <c r="AC8" s="1"/>
       <c r="AD8" s="1"/>
       <c r="AE8" s="1"/>
-    </row>
-    <row r="9" spans="1:31">
-      <c r="A9" s="4" t="s">
+      <c r="AF8" s="3"/>
+    </row>
+    <row r="9" spans="1:32">
+      <c r="A9" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C9" s="1"/>
@@ -2352,7 +2597,9 @@
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
+      <c r="J9" s="13" t="s">
+        <v>83</v>
+      </c>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
@@ -2374,12 +2621,13 @@
       <c r="AC9" s="1"/>
       <c r="AD9" s="1"/>
       <c r="AE9" s="1"/>
-    </row>
-    <row r="10" spans="1:31">
-      <c r="A10" s="4" t="s">
+      <c r="AF9" s="3"/>
+    </row>
+    <row r="10" spans="1:32">
+      <c r="A10" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="12" t="s">
         <v>22</v>
       </c>
       <c r="C10" s="1"/>
@@ -2389,7 +2637,9 @@
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
+      <c r="J10" s="13" t="s">
+        <v>84</v>
+      </c>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -2411,12 +2661,13 @@
       <c r="AC10" s="1"/>
       <c r="AD10" s="1"/>
       <c r="AE10" s="1"/>
-    </row>
-    <row r="11" spans="1:31">
-      <c r="A11" s="4" t="s">
+      <c r="AF10" s="3"/>
+    </row>
+    <row r="11" spans="1:32">
+      <c r="A11" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="12" t="s">
         <v>23</v>
       </c>
       <c r="C11" s="1"/>
@@ -2426,7 +2677,9 @@
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
+      <c r="J11" s="13" t="s">
+        <v>85</v>
+      </c>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
@@ -2448,8 +2701,9 @@
       <c r="AC11" s="1"/>
       <c r="AD11" s="1"/>
       <c r="AE11" s="1"/>
-    </row>
-    <row r="12" spans="1:31">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -2459,7 +2713,9 @@
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
+      <c r="J12" s="13" t="s">
+        <v>86</v>
+      </c>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
@@ -2481,202 +2737,393 @@
       <c r="AC12" s="1"/>
       <c r="AD12" s="1"/>
       <c r="AE12" s="1"/>
-    </row>
-    <row r="13" spans="1:31">
-      <c r="A13" s="4" t="s">
+      <c r="AF12" s="3"/>
+    </row>
+    <row r="13" spans="1:32">
+      <c r="A13" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="14" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="14" spans="1:31">
-      <c r="A14" s="4" t="s">
+      <c r="J13" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="AF13" s="3"/>
+    </row>
+    <row r="14" spans="1:32">
+      <c r="A14" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="15" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="15" spans="1:31">
-      <c r="A15" s="4" t="s">
+      <c r="J14" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="AF14" s="3"/>
+    </row>
+    <row r="15" spans="1:32">
+      <c r="A15" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="15" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="16" spans="1:31">
-      <c r="A16" s="4" t="s">
+      <c r="J15" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="AF15" s="3"/>
+    </row>
+    <row r="16" spans="1:32">
+      <c r="A16" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="15" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="4" t="s">
+      <c r="J16" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="1:32">
+      <c r="A17" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="15" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="4" t="s">
+      <c r="J17" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="AF17" s="3"/>
+    </row>
+    <row r="18" spans="1:32">
+      <c r="A18" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="15" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="4" t="s">
+      <c r="J18" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AF18" s="3"/>
+    </row>
+    <row r="19" spans="1:32">
+      <c r="A19" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="15" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="4" t="s">
+      <c r="J19" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="1:32">
+      <c r="A20" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="15" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="4" t="s">
+      <c r="J20" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="AF20" s="3"/>
+    </row>
+    <row r="21" spans="1:32">
+      <c r="A21" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="15" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" s="4" t="s">
+      <c r="J21" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="AF21" s="3"/>
+    </row>
+    <row r="22" spans="1:32">
+      <c r="J22" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="AF22" s="3"/>
+    </row>
+    <row r="23" spans="1:32">
+      <c r="A23" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="16" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="4" t="s">
+      <c r="J23" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="AF23" s="3"/>
+    </row>
+    <row r="24" spans="1:32">
+      <c r="A24" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="16" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="4" t="s">
+      <c r="J24" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="AF24" s="3"/>
+    </row>
+    <row r="25" spans="1:32">
+      <c r="A25" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="16" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="4" t="s">
+      <c r="J25" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="AF25" s="3"/>
+    </row>
+    <row r="26" spans="1:32">
+      <c r="A26" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="16" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" s="4" t="s">
+      <c r="J26" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="AF26" s="3"/>
+    </row>
+    <row r="27" spans="1:32">
+      <c r="A27" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="16" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28" s="4" t="s">
+      <c r="J27" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="AF27" s="3"/>
+    </row>
+    <row r="28" spans="1:32">
+      <c r="A28" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="16" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29" s="4" t="s">
+      <c r="J28" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="AF28" s="3"/>
+    </row>
+    <row r="29" spans="1:32">
+      <c r="A29" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="16" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30" s="4" t="s">
+      <c r="J29" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF29" s="3"/>
+    </row>
+    <row r="30" spans="1:32">
+      <c r="A30" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="16" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31" s="6"/>
-      <c r="B31" s="6"/>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32" s="4" t="s">
+      <c r="J30" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="AF30" s="3"/>
+    </row>
+    <row r="31" spans="1:32">
+      <c r="A31" s="4"/>
+      <c r="B31" s="4"/>
+      <c r="J31" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="AF31" s="3"/>
+    </row>
+    <row r="32" spans="1:32">
+      <c r="A32" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="17" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33" s="4" t="s">
+      <c r="J32" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="AF32" s="3"/>
+    </row>
+    <row r="33" spans="1:32">
+      <c r="A33" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="17" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" s="4" t="s">
+      <c r="J33" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="AF33" s="3"/>
+    </row>
+    <row r="34" spans="1:32">
+      <c r="A34" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="17" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35" s="4" t="s">
+      <c r="J34" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="AF34" s="3"/>
+    </row>
+    <row r="35" spans="1:32">
+      <c r="A35" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="17" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36" s="4" t="s">
+      <c r="J35" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="AF35" s="3"/>
+    </row>
+    <row r="36" spans="1:32">
+      <c r="A36" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="17" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" s="4" t="s">
+      <c r="J36" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF36" s="3"/>
+    </row>
+    <row r="37" spans="1:32">
+      <c r="A37" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="17" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38" s="4" t="s">
+      <c r="J37" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="AF37" s="3"/>
+    </row>
+    <row r="38" spans="1:32">
+      <c r="A38" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="17" t="s">
         <v>68</v>
       </c>
+      <c r="J38" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="AF38" s="3"/>
+    </row>
+    <row r="39" spans="1:32">
+      <c r="J39" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="1:32">
+      <c r="J40" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="1:32">
+      <c r="J41" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="AF41" s="3"/>
+    </row>
+    <row r="42" spans="1:32">
+      <c r="J42" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="AF42" s="3"/>
+    </row>
+    <row r="43" spans="1:32">
+      <c r="J43" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="AF43" s="3"/>
+    </row>
+    <row r="44" spans="1:32">
+      <c r="J44" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="AF44" s="3"/>
+    </row>
+    <row r="45" spans="1:32">
+      <c r="J45" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="AF45" s="3"/>
+    </row>
+    <row r="46" spans="1:32">
+      <c r="J46" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="AF46" s="3"/>
+    </row>
+    <row r="47" spans="1:32">
+      <c r="J47" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="AF47" s="3"/>
+    </row>
+    <row r="48" spans="1:32">
+      <c r="J48" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="AF48" s="3"/>
+    </row>
+    <row r="49" spans="10:32">
+      <c r="J49" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="AF49" s="3"/>
+    </row>
+    <row r="50" spans="10:32">
+      <c r="J50" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="AF50" s="3"/>
+    </row>
+    <row r="51" spans="10:32">
+      <c r="J51" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF51" s="3"/>
+    </row>
+    <row r="52" spans="10:32">
+      <c r="J52" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="AF52" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="81" type="noConversion"/>

--- a/frontend/public/formats/physical_format.xlsx
+++ b/frontend/public/formats/physical_format.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PROJECTS FOLDER\SG ENCON\frontend\public\formats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{996B7389-E052-48DD-9A82-4E179DD57ED0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5E25E28-FA8B-4CA1-8E1B-76A402D7639B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -278,42 +278,9 @@
     <t>Not Required</t>
   </si>
   <si>
-    <t>Admin Head</t>
-  </si>
-  <si>
-    <t>Analyst-Fiber</t>
-  </si>
-  <si>
-    <t>Analyst-Fttx</t>
-  </si>
-  <si>
-    <t>Analyst-IPCOLO</t>
-  </si>
-  <si>
-    <t>Analyst-ISP</t>
-  </si>
-  <si>
-    <t>Analyst-Material</t>
-  </si>
-  <si>
-    <t>Analyst-Planning</t>
-  </si>
-  <si>
-    <t>Analyst-PMO</t>
-  </si>
-  <si>
-    <t>Analyst-Power &amp; Fuel</t>
-  </si>
-  <si>
-    <t>Analyst-Utility</t>
-  </si>
-  <si>
     <t>Assistant Splicer</t>
   </si>
   <si>
-    <t>CMP LEAD</t>
-  </si>
-  <si>
     <t>Commercial Executive</t>
   </si>
   <si>
@@ -329,63 +296,24 @@
     <t>Fiber SME</t>
   </si>
   <si>
-    <t>Fibre Supervisor</t>
-  </si>
-  <si>
     <t>FRT Helper</t>
   </si>
   <si>
-    <t>Fttx Assistant Splicer</t>
-  </si>
-  <si>
-    <t>Fttx Engineer</t>
-  </si>
-  <si>
-    <t>Fttx Helper</t>
-  </si>
-  <si>
-    <t>Fttx Lead</t>
-  </si>
-  <si>
-    <t>Fttx Splicer</t>
-  </si>
-  <si>
-    <t>Fttx Supervisor</t>
-  </si>
-  <si>
-    <t>Fttx Technician</t>
-  </si>
-  <si>
     <t>HR Executive</t>
   </si>
   <si>
     <t>ISP Engineer</t>
   </si>
   <si>
-    <t>Legal Executive</t>
-  </si>
-  <si>
-    <t>MIS Executive</t>
-  </si>
-  <si>
     <t>Office Helper</t>
   </si>
   <si>
     <t>OMCR Lead</t>
   </si>
   <si>
-    <t>OMCR Resources</t>
-  </si>
-  <si>
-    <t>Other Roles - Temporary Technician</t>
-  </si>
-  <si>
     <t>Patroller</t>
   </si>
   <si>
-    <t>Project Technician</t>
-  </si>
-  <si>
     <t>Rigger</t>
   </si>
   <si>
@@ -401,18 +329,9 @@
     <t>State HR Head</t>
   </si>
   <si>
-    <t>State HSEF Officer</t>
-  </si>
-  <si>
     <t>State ISP SME</t>
   </si>
   <si>
-    <t>State Material Manager</t>
-  </si>
-  <si>
-    <t>State Operation Head</t>
-  </si>
-  <si>
     <t>State Utility SME</t>
   </si>
   <si>
@@ -425,10 +344,91 @@
     <t>Utility Supervisor</t>
   </si>
   <si>
-    <t>Warehouse Helper</t>
-  </si>
-  <si>
-    <t>Warehouse Incharge Cum Security</t>
+    <t>FTTx Technician</t>
+  </si>
+  <si>
+    <t>FTTx Engineer</t>
+  </si>
+  <si>
+    <t>Analyst</t>
+  </si>
+  <si>
+    <t>FTTx Splicer</t>
+  </si>
+  <si>
+    <t>NOC Executive</t>
+  </si>
+  <si>
+    <t>FTTx Supervisor</t>
+  </si>
+  <si>
+    <t>Fiber Supervisor</t>
+  </si>
+  <si>
+    <t>CMP Lead</t>
+  </si>
+  <si>
+    <t>FTTx Assistant Splicer</t>
+  </si>
+  <si>
+    <t>HSEF LEAD</t>
+  </si>
+  <si>
+    <t>Circle Head</t>
+  </si>
+  <si>
+    <t>WAREHOUSE SECURITY GUARD</t>
+  </si>
+  <si>
+    <t>WH Helper</t>
+  </si>
+  <si>
+    <t>Project technician</t>
+  </si>
+  <si>
+    <t>FTTx Helper</t>
+  </si>
+  <si>
+    <t>FTTx Lead</t>
+  </si>
+  <si>
+    <t>ADMIN LEAD</t>
+  </si>
+  <si>
+    <t>ODSC Supevisor</t>
+  </si>
+  <si>
+    <t>NOC LEAD</t>
+  </si>
+  <si>
+    <t>QUALITY &amp; PLANING HEAD</t>
+  </si>
+  <si>
+    <t>UTILITY CO-ORODINATOR</t>
+  </si>
+  <si>
+    <t>OFFICE BOY</t>
+  </si>
+  <si>
+    <t>HR HEAD</t>
+  </si>
+  <si>
+    <t>PROJECT LEAD</t>
+  </si>
+  <si>
+    <t>FTTX SME</t>
+  </si>
+  <si>
+    <t>ASSISTANT HR MANAGER</t>
+  </si>
+  <si>
+    <t>MATERIAL LEAD</t>
+  </si>
+  <si>
+    <t>HR MANAGER</t>
+  </si>
+  <si>
+    <t>O &amp; M HEAD</t>
   </si>
 </sst>
 </file>
@@ -2302,7 +2302,7 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="9" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
@@ -2348,7 +2348,7 @@
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="13" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
@@ -2394,7 +2394,7 @@
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="13" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
@@ -2438,7 +2438,7 @@
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="13" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
@@ -2478,7 +2478,7 @@
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="13" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
@@ -2558,7 +2558,7 @@
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="J8" s="13" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
@@ -2598,7 +2598,7 @@
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
       <c r="J9" s="13" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
@@ -2638,7 +2638,7 @@
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="13" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
@@ -2678,7 +2678,7 @@
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
       <c r="J11" s="13" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
@@ -2714,7 +2714,7 @@
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
       <c r="J12" s="13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
@@ -2747,7 +2747,7 @@
         <v>43</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="AF13" s="3"/>
     </row>
@@ -2759,7 +2759,7 @@
         <v>44</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="AF14" s="3"/>
     </row>
@@ -2771,7 +2771,7 @@
         <v>45</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="AF15" s="3"/>
     </row>
@@ -2783,7 +2783,7 @@
         <v>46</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="AF16" s="3"/>
     </row>
@@ -2795,7 +2795,7 @@
         <v>47</v>
       </c>
       <c r="J17" s="13" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="AF17" s="3"/>
     </row>
@@ -2807,7 +2807,7 @@
         <v>48</v>
       </c>
       <c r="J18" s="13" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="AF18" s="3"/>
     </row>
@@ -2819,7 +2819,7 @@
         <v>49</v>
       </c>
       <c r="J19" s="13" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="AF19" s="3"/>
     </row>
@@ -2831,7 +2831,7 @@
         <v>50</v>
       </c>
       <c r="J20" s="13" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="AF20" s="3"/>
     </row>
@@ -2843,13 +2843,13 @@
         <v>51</v>
       </c>
       <c r="J21" s="13" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="AF21" s="3"/>
     </row>
     <row r="22" spans="1:32">
       <c r="J22" s="13" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="AF22" s="3"/>
     </row>
@@ -2861,7 +2861,7 @@
         <v>53</v>
       </c>
       <c r="J23" s="13" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="AF23" s="3"/>
     </row>
@@ -2873,7 +2873,7 @@
         <v>54</v>
       </c>
       <c r="J24" s="13" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="AF24" s="3"/>
     </row>
@@ -2885,7 +2885,7 @@
         <v>55</v>
       </c>
       <c r="J25" s="13" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="AF25" s="3"/>
     </row>
@@ -2897,7 +2897,7 @@
         <v>56</v>
       </c>
       <c r="J26" s="13" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="AF26" s="3"/>
     </row>
@@ -2909,7 +2909,7 @@
         <v>57</v>
       </c>
       <c r="J27" s="13" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="AF27" s="3"/>
     </row>
@@ -2921,7 +2921,7 @@
         <v>58</v>
       </c>
       <c r="J28" s="13" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="AF28" s="3"/>
     </row>
@@ -2933,7 +2933,7 @@
         <v>59</v>
       </c>
       <c r="J29" s="13" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="AF29" s="3"/>
     </row>
@@ -2945,7 +2945,7 @@
         <v>60</v>
       </c>
       <c r="J30" s="13" t="s">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="AF30" s="3"/>
     </row>
@@ -2953,7 +2953,7 @@
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="J31" s="13" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="AF31" s="3"/>
     </row>
@@ -2965,7 +2965,7 @@
         <v>62</v>
       </c>
       <c r="J32" s="13" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="AF32" s="3"/>
     </row>
@@ -2977,7 +2977,7 @@
         <v>63</v>
       </c>
       <c r="J33" s="13" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="AF33" s="3"/>
     </row>
@@ -2989,7 +2989,7 @@
         <v>64</v>
       </c>
       <c r="J34" s="13" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="AF34" s="3"/>
     </row>
@@ -3001,7 +3001,7 @@
         <v>65</v>
       </c>
       <c r="J35" s="13" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="AF35" s="3"/>
     </row>
@@ -3013,7 +3013,7 @@
         <v>66</v>
       </c>
       <c r="J36" s="13" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="AF36" s="3"/>
     </row>
@@ -3025,7 +3025,7 @@
         <v>67</v>
       </c>
       <c r="J37" s="13" t="s">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="AF37" s="3"/>
     </row>
@@ -3037,25 +3037,25 @@
         <v>68</v>
       </c>
       <c r="J38" s="13" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AF38" s="3"/>
     </row>
     <row r="39" spans="1:32">
       <c r="J39" s="13" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AF39" s="3"/>
     </row>
     <row r="40" spans="1:32">
       <c r="J40" s="13" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AF40" s="3"/>
     </row>
     <row r="41" spans="1:32">
       <c r="J41" s="13" t="s">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="AF41" s="3"/>
     </row>

--- a/frontend/public/formats/physical_format.xlsx
+++ b/frontend/public/formats/physical_format.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PROJECTS FOLDER\SG ENCON\frontend\public\formats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5E25E28-FA8B-4CA1-8E1B-76A402D7639B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67F435DF-C050-42BB-ABFC-F5CF4FB29C7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="129">
   <si>
     <t>Cluster</t>
   </si>
@@ -429,6 +429,12 @@
   </si>
   <si>
     <t>O &amp; M HEAD</t>
+  </si>
+  <si>
+    <t>GTLI</t>
+  </si>
+  <si>
+    <t>Covered</t>
   </si>
 </sst>
 </file>
@@ -1010,6 +1016,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
@@ -1031,7 +1038,7 @@
       <family val="3"/>
     </font>
   </fonts>
-  <fills count="40">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1250,6 +1257,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1605,7 +1618,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="82" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="204" applyFont="1"/>
     <xf numFmtId="9" fontId="74" fillId="0" borderId="0" xfId="204" applyFont="1" applyAlignment="1">
@@ -1636,6 +1649,8 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="35" borderId="1" xfId="204" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="39" borderId="1" xfId="204" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="53" fillId="33" borderId="1" xfId="204" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="53" fillId="40" borderId="0" xfId="204" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="205">
     <cellStyle name="20% - Accent1" xfId="41" builtinId="30" customBuiltin="1"/>
@@ -2151,7 +2166,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{669DF689-B0D6-46EA-ACFD-66E425F22CA2}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AF52"/>
+  <dimension ref="A1:AG52"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="7.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -2181,15 +2196,16 @@
     <col min="25" max="25" width="9.109375" style="3" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="15.109375" style="3" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="7.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="7.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="9.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="8" style="2" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="8.77734375" style="2"/>
-    <col min="33" max="16384" width="8.77734375" style="3"/>
+    <col min="28" max="28" width="12.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="7.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="9.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="8.77734375" style="2"/>
+    <col min="34" max="16384" width="8.77734375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32">
+    <row r="1" spans="1:33">
       <c r="A1" s="5" t="s">
         <v>12</v>
       </c>
@@ -2271,21 +2287,24 @@
       <c r="AA1" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="AB1" s="5" t="s">
+      <c r="AB1" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="AC1" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="AC1" s="5" t="s">
+      <c r="AD1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="AD1" s="5" t="s">
+      <c r="AE1" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="AE1" s="5" t="s">
+      <c r="AF1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="AF1" s="3"/>
-    </row>
-    <row r="2" spans="1:32">
+      <c r="AG1" s="3"/>
+    </row>
+    <row r="2" spans="1:33">
       <c r="A2" s="7" t="s">
         <v>24</v>
       </c>
@@ -2325,13 +2344,16 @@
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
       <c r="AA2" s="1"/>
-      <c r="AB2" s="1"/>
+      <c r="AB2" s="19" t="s">
+        <v>128</v>
+      </c>
       <c r="AC2" s="1"/>
       <c r="AD2" s="1"/>
       <c r="AE2" s="1"/>
-      <c r="AF2" s="3"/>
-    </row>
-    <row r="3" spans="1:32">
+      <c r="AF2" s="1"/>
+      <c r="AG2" s="3"/>
+    </row>
+    <row r="3" spans="1:33">
       <c r="A3" s="12" t="s">
         <v>24</v>
       </c>
@@ -2371,13 +2393,16 @@
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
       <c r="AA3" s="1"/>
-      <c r="AB3" s="1"/>
+      <c r="AB3" s="19" t="s">
+        <v>71</v>
+      </c>
       <c r="AC3" s="1"/>
       <c r="AD3" s="1"/>
       <c r="AE3" s="1"/>
-      <c r="AF3" s="3"/>
-    </row>
-    <row r="4" spans="1:32">
+      <c r="AF3" s="1"/>
+      <c r="AG3" s="3"/>
+    </row>
+    <row r="4" spans="1:33">
       <c r="A4" s="12" t="s">
         <v>24</v>
       </c>
@@ -2415,13 +2440,16 @@
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
       <c r="AA4" s="1"/>
-      <c r="AB4" s="1"/>
+      <c r="AB4" s="19" t="s">
+        <v>72</v>
+      </c>
       <c r="AC4" s="1"/>
       <c r="AD4" s="1"/>
       <c r="AE4" s="1"/>
-      <c r="AF4" s="3"/>
-    </row>
-    <row r="5" spans="1:32">
+      <c r="AF4" s="1"/>
+      <c r="AG4" s="3"/>
+    </row>
+    <row r="5" spans="1:33">
       <c r="A5" s="12" t="s">
         <v>24</v>
       </c>
@@ -2461,9 +2489,10 @@
       <c r="AC5" s="1"/>
       <c r="AD5" s="1"/>
       <c r="AE5" s="1"/>
-      <c r="AF5" s="3"/>
-    </row>
-    <row r="6" spans="1:32">
+      <c r="AF5" s="1"/>
+      <c r="AG5" s="3"/>
+    </row>
+    <row r="6" spans="1:33">
       <c r="A6" s="12" t="s">
         <v>24</v>
       </c>
@@ -2501,9 +2530,10 @@
       <c r="AC6" s="1"/>
       <c r="AD6" s="1"/>
       <c r="AE6" s="1"/>
-      <c r="AF6" s="3"/>
-    </row>
-    <row r="7" spans="1:32">
+      <c r="AF6" s="1"/>
+      <c r="AG6" s="3"/>
+    </row>
+    <row r="7" spans="1:33">
       <c r="A7" s="12" t="s">
         <v>24</v>
       </c>
@@ -2541,9 +2571,10 @@
       <c r="AC7" s="1"/>
       <c r="AD7" s="1"/>
       <c r="AE7" s="1"/>
-      <c r="AF7" s="3"/>
-    </row>
-    <row r="8" spans="1:32">
+      <c r="AF7" s="1"/>
+      <c r="AG7" s="3"/>
+    </row>
+    <row r="8" spans="1:33">
       <c r="A8" s="12" t="s">
         <v>24</v>
       </c>
@@ -2581,9 +2612,10 @@
       <c r="AC8" s="1"/>
       <c r="AD8" s="1"/>
       <c r="AE8" s="1"/>
-      <c r="AF8" s="3"/>
-    </row>
-    <row r="9" spans="1:32">
+      <c r="AF8" s="1"/>
+      <c r="AG8" s="3"/>
+    </row>
+    <row r="9" spans="1:33">
       <c r="A9" s="12" t="s">
         <v>24</v>
       </c>
@@ -2621,9 +2653,10 @@
       <c r="AC9" s="1"/>
       <c r="AD9" s="1"/>
       <c r="AE9" s="1"/>
-      <c r="AF9" s="3"/>
-    </row>
-    <row r="10" spans="1:32">
+      <c r="AF9" s="1"/>
+      <c r="AG9" s="3"/>
+    </row>
+    <row r="10" spans="1:33">
       <c r="A10" s="12" t="s">
         <v>24</v>
       </c>
@@ -2661,9 +2694,10 @@
       <c r="AC10" s="1"/>
       <c r="AD10" s="1"/>
       <c r="AE10" s="1"/>
-      <c r="AF10" s="3"/>
-    </row>
-    <row r="11" spans="1:32">
+      <c r="AF10" s="1"/>
+      <c r="AG10" s="3"/>
+    </row>
+    <row r="11" spans="1:33">
       <c r="A11" s="12" t="s">
         <v>24</v>
       </c>
@@ -2701,9 +2735,10 @@
       <c r="AC11" s="1"/>
       <c r="AD11" s="1"/>
       <c r="AE11" s="1"/>
-      <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32">
+      <c r="AF11" s="1"/>
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -2737,9 +2772,10 @@
       <c r="AC12" s="1"/>
       <c r="AD12" s="1"/>
       <c r="AE12" s="1"/>
-      <c r="AF12" s="3"/>
-    </row>
-    <row r="13" spans="1:32">
+      <c r="AF12" s="1"/>
+      <c r="AG12" s="3"/>
+    </row>
+    <row r="13" spans="1:33">
       <c r="A13" s="14" t="s">
         <v>42</v>
       </c>
@@ -2749,9 +2785,9 @@
       <c r="J13" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="AF13" s="3"/>
-    </row>
-    <row r="14" spans="1:32">
+      <c r="AG13" s="3"/>
+    </row>
+    <row r="14" spans="1:33">
       <c r="A14" s="14" t="s">
         <v>42</v>
       </c>
@@ -2761,9 +2797,9 @@
       <c r="J14" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="AF14" s="3"/>
-    </row>
-    <row r="15" spans="1:32">
+      <c r="AG14" s="3"/>
+    </row>
+    <row r="15" spans="1:33">
       <c r="A15" s="14" t="s">
         <v>42</v>
       </c>
@@ -2773,9 +2809,9 @@
       <c r="J15" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="AF15" s="3"/>
-    </row>
-    <row r="16" spans="1:32">
+      <c r="AG15" s="3"/>
+    </row>
+    <row r="16" spans="1:33">
       <c r="A16" s="14" t="s">
         <v>42</v>
       </c>
@@ -2785,9 +2821,9 @@
       <c r="J16" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="1:32">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="1:33">
       <c r="A17" s="14" t="s">
         <v>42</v>
       </c>
@@ -2797,9 +2833,9 @@
       <c r="J17" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="AF17" s="3"/>
-    </row>
-    <row r="18" spans="1:32">
+      <c r="AG17" s="3"/>
+    </row>
+    <row r="18" spans="1:33">
       <c r="A18" s="14" t="s">
         <v>42</v>
       </c>
@@ -2809,9 +2845,9 @@
       <c r="J18" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="AF18" s="3"/>
-    </row>
-    <row r="19" spans="1:32">
+      <c r="AG18" s="3"/>
+    </row>
+    <row r="19" spans="1:33">
       <c r="A19" s="14" t="s">
         <v>42</v>
       </c>
@@ -2821,9 +2857,9 @@
       <c r="J19" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="1:32">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="1:33">
       <c r="A20" s="14" t="s">
         <v>42</v>
       </c>
@@ -2833,9 +2869,9 @@
       <c r="J20" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="AF20" s="3"/>
-    </row>
-    <row r="21" spans="1:32">
+      <c r="AG20" s="3"/>
+    </row>
+    <row r="21" spans="1:33">
       <c r="A21" s="14" t="s">
         <v>42</v>
       </c>
@@ -2845,15 +2881,15 @@
       <c r="J21" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="AF21" s="3"/>
-    </row>
-    <row r="22" spans="1:32">
+      <c r="AG21" s="3"/>
+    </row>
+    <row r="22" spans="1:33">
       <c r="J22" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="AF22" s="3"/>
-    </row>
-    <row r="23" spans="1:32">
+      <c r="AG22" s="3"/>
+    </row>
+    <row r="23" spans="1:33">
       <c r="A23" s="16" t="s">
         <v>52</v>
       </c>
@@ -2863,9 +2899,9 @@
       <c r="J23" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AF23" s="3"/>
-    </row>
-    <row r="24" spans="1:32">
+      <c r="AG23" s="3"/>
+    </row>
+    <row r="24" spans="1:33">
       <c r="A24" s="16" t="s">
         <v>52</v>
       </c>
@@ -2875,9 +2911,9 @@
       <c r="J24" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="AF24" s="3"/>
-    </row>
-    <row r="25" spans="1:32">
+      <c r="AG24" s="3"/>
+    </row>
+    <row r="25" spans="1:33">
       <c r="A25" s="16" t="s">
         <v>52</v>
       </c>
@@ -2887,9 +2923,9 @@
       <c r="J25" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="AF25" s="3"/>
-    </row>
-    <row r="26" spans="1:32">
+      <c r="AG25" s="3"/>
+    </row>
+    <row r="26" spans="1:33">
       <c r="A26" s="16" t="s">
         <v>52</v>
       </c>
@@ -2899,9 +2935,9 @@
       <c r="J26" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="AF26" s="3"/>
-    </row>
-    <row r="27" spans="1:32">
+      <c r="AG26" s="3"/>
+    </row>
+    <row r="27" spans="1:33">
       <c r="A27" s="16" t="s">
         <v>52</v>
       </c>
@@ -2911,9 +2947,9 @@
       <c r="J27" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="AF27" s="3"/>
-    </row>
-    <row r="28" spans="1:32">
+      <c r="AG27" s="3"/>
+    </row>
+    <row r="28" spans="1:33">
       <c r="A28" s="16" t="s">
         <v>52</v>
       </c>
@@ -2923,9 +2959,9 @@
       <c r="J28" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="AF28" s="3"/>
-    </row>
-    <row r="29" spans="1:32">
+      <c r="AG28" s="3"/>
+    </row>
+    <row r="29" spans="1:33">
       <c r="A29" s="16" t="s">
         <v>52</v>
       </c>
@@ -2935,9 +2971,9 @@
       <c r="J29" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="AF29" s="3"/>
-    </row>
-    <row r="30" spans="1:32">
+      <c r="AG29" s="3"/>
+    </row>
+    <row r="30" spans="1:33">
       <c r="A30" s="16" t="s">
         <v>52</v>
       </c>
@@ -2947,17 +2983,17 @@
       <c r="J30" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="AF30" s="3"/>
-    </row>
-    <row r="31" spans="1:32">
+      <c r="AG30" s="3"/>
+    </row>
+    <row r="31" spans="1:33">
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="J31" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="AF31" s="3"/>
-    </row>
-    <row r="32" spans="1:32">
+      <c r="AG31" s="3"/>
+    </row>
+    <row r="32" spans="1:33">
       <c r="A32" s="17" t="s">
         <v>61</v>
       </c>
@@ -2967,9 +3003,9 @@
       <c r="J32" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="AF32" s="3"/>
-    </row>
-    <row r="33" spans="1:32">
+      <c r="AG32" s="3"/>
+    </row>
+    <row r="33" spans="1:33">
       <c r="A33" s="17" t="s">
         <v>61</v>
       </c>
@@ -2979,9 +3015,9 @@
       <c r="J33" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="AF33" s="3"/>
-    </row>
-    <row r="34" spans="1:32">
+      <c r="AG33" s="3"/>
+    </row>
+    <row r="34" spans="1:33">
       <c r="A34" s="17" t="s">
         <v>61</v>
       </c>
@@ -2991,9 +3027,9 @@
       <c r="J34" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AF34" s="3"/>
-    </row>
-    <row r="35" spans="1:32">
+      <c r="AG34" s="3"/>
+    </row>
+    <row r="35" spans="1:33">
       <c r="A35" s="17" t="s">
         <v>61</v>
       </c>
@@ -3003,9 +3039,9 @@
       <c r="J35" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="AF35" s="3"/>
-    </row>
-    <row r="36" spans="1:32">
+      <c r="AG35" s="3"/>
+    </row>
+    <row r="36" spans="1:33">
       <c r="A36" s="17" t="s">
         <v>61</v>
       </c>
@@ -3015,9 +3051,9 @@
       <c r="J36" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="AF36" s="3"/>
-    </row>
-    <row r="37" spans="1:32">
+      <c r="AG36" s="3"/>
+    </row>
+    <row r="37" spans="1:33">
       <c r="A37" s="17" t="s">
         <v>61</v>
       </c>
@@ -3027,9 +3063,9 @@
       <c r="J37" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="AF37" s="3"/>
-    </row>
-    <row r="38" spans="1:32">
+      <c r="AG37" s="3"/>
+    </row>
+    <row r="38" spans="1:33">
       <c r="A38" s="17" t="s">
         <v>61</v>
       </c>
@@ -3039,91 +3075,91 @@
       <c r="J38" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="AF38" s="3"/>
-    </row>
-    <row r="39" spans="1:32">
+      <c r="AG38" s="3"/>
+    </row>
+    <row r="39" spans="1:33">
       <c r="J39" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="1:32">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="1:33">
       <c r="J40" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="1:32">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="1:33">
       <c r="J41" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="AF41" s="3"/>
-    </row>
-    <row r="42" spans="1:32">
+      <c r="AG41" s="3"/>
+    </row>
+    <row r="42" spans="1:33">
       <c r="J42" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="AF42" s="3"/>
-    </row>
-    <row r="43" spans="1:32">
+      <c r="AG42" s="3"/>
+    </row>
+    <row r="43" spans="1:33">
       <c r="J43" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="AF43" s="3"/>
-    </row>
-    <row r="44" spans="1:32">
+      <c r="AG43" s="3"/>
+    </row>
+    <row r="44" spans="1:33">
       <c r="J44" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="AF44" s="3"/>
-    </row>
-    <row r="45" spans="1:32">
+      <c r="AG44" s="3"/>
+    </row>
+    <row r="45" spans="1:33">
       <c r="J45" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="AF45" s="3"/>
-    </row>
-    <row r="46" spans="1:32">
+      <c r="AG45" s="3"/>
+    </row>
+    <row r="46" spans="1:33">
       <c r="J46" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="AF46" s="3"/>
-    </row>
-    <row r="47" spans="1:32">
+      <c r="AG46" s="3"/>
+    </row>
+    <row r="47" spans="1:33">
       <c r="J47" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="AF47" s="3"/>
-    </row>
-    <row r="48" spans="1:32">
+      <c r="AG47" s="3"/>
+    </row>
+    <row r="48" spans="1:33">
       <c r="J48" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="AF48" s="3"/>
-    </row>
-    <row r="49" spans="10:32">
+      <c r="AG48" s="3"/>
+    </row>
+    <row r="49" spans="10:33">
       <c r="J49" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="AF49" s="3"/>
-    </row>
-    <row r="50" spans="10:32">
+      <c r="AG49" s="3"/>
+    </row>
+    <row r="50" spans="10:33">
       <c r="J50" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="AF50" s="3"/>
-    </row>
-    <row r="51" spans="10:32">
+      <c r="AG50" s="3"/>
+    </row>
+    <row r="51" spans="10:33">
       <c r="J51" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="AF51" s="3"/>
-    </row>
-    <row r="52" spans="10:32">
+      <c r="AG51" s="3"/>
+    </row>
+    <row r="52" spans="10:33">
       <c r="J52" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="AF52" s="3"/>
+      <c r="AG52" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="81" type="noConversion"/>

--- a/frontend/public/formats/physical_format.xlsx
+++ b/frontend/public/formats/physical_format.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PROJECTS FOLDER\SG ENCON\frontend\public\formats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67F435DF-C050-42BB-ABFC-F5CF4FB29C7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63097CD8-1954-4524-AAAE-83631F32431B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="167">
   <si>
     <t>Cluster</t>
   </si>
@@ -383,9 +383,6 @@
     <t>WH Helper</t>
   </si>
   <si>
-    <t>Project technician</t>
-  </si>
-  <si>
     <t>FTTx Helper</t>
   </si>
   <si>
@@ -435,6 +432,123 @@
   </si>
   <si>
     <t>Covered</t>
+  </si>
+  <si>
+    <t>Project Technician</t>
+  </si>
+  <si>
+    <t>Fiber Engineer</t>
+  </si>
+  <si>
+    <t>Utility Engineer</t>
+  </si>
+  <si>
+    <t>State Planning Manager</t>
+  </si>
+  <si>
+    <t>Warehouse Incharge</t>
+  </si>
+  <si>
+    <t>State Operation Head</t>
+  </si>
+  <si>
+    <t>State Material Manager</t>
+  </si>
+  <si>
+    <t>State Energy Manager</t>
+  </si>
+  <si>
+    <t>Quality Lead</t>
+  </si>
+  <si>
+    <t>State Fiber Head</t>
+  </si>
+  <si>
+    <t>State HSEF Officer</t>
+  </si>
+  <si>
+    <t>State FTTx SME</t>
+  </si>
+  <si>
+    <t>Warehouse Incharge Cum Security</t>
+  </si>
+  <si>
+    <t>Warehouse Helper</t>
+  </si>
+  <si>
+    <t>MIS Executive</t>
+  </si>
+  <si>
+    <t>PROJECT MIS</t>
+  </si>
+  <si>
+    <t>OMCR Resources</t>
+  </si>
+  <si>
+    <t>Analyst - Material</t>
+  </si>
+  <si>
+    <t>Analyst - Utility</t>
+  </si>
+  <si>
+    <t>Analyst - Planning</t>
+  </si>
+  <si>
+    <t>Analyst - Power &amp; Fuel</t>
+  </si>
+  <si>
+    <t>Analyst - Ipcolo</t>
+  </si>
+  <si>
+    <t>Analyst - ISP</t>
+  </si>
+  <si>
+    <t>Analyst - PMO</t>
+  </si>
+  <si>
+    <t>Analyst - Fttx</t>
+  </si>
+  <si>
+    <t>Analyst - Fiber</t>
+  </si>
+  <si>
+    <t>Analyst - D2D</t>
+  </si>
+  <si>
+    <t>Analyst - HSEF</t>
+  </si>
+  <si>
+    <t>Asst Fiber SME</t>
+  </si>
+  <si>
+    <t>Utility SME</t>
+  </si>
+  <si>
+    <t>Utility MIS Coordinator</t>
+  </si>
+  <si>
+    <t>MIS Coordinator</t>
+  </si>
+  <si>
+    <t>Legal Executive</t>
+  </si>
+  <si>
+    <t>Legal Advisor</t>
+  </si>
+  <si>
+    <t>Project Head</t>
+  </si>
+  <si>
+    <t>Material Helper</t>
+  </si>
+  <si>
+    <t>Material Cordinator</t>
+  </si>
+  <si>
+    <t>Analyst MIS</t>
+  </si>
+  <si>
+    <t>Zonal Fiber SME</t>
   </si>
 </sst>
 </file>
@@ -445,7 +559,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;₹&quot;\ * #,##0.00_ ;_ &quot;₹&quot;\ * \-#,##0.00_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="86">
+  <fonts count="84">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1025,20 +1139,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF0A3069"/>
-      <name val="Consolas"/>
-      <family val="3"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF1F2328"/>
-      <name val="Consolas"/>
-      <family val="3"/>
-    </font>
   </fonts>
-  <fills count="41">
+  <fills count="42">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1263,6 +1365,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1618,7 +1726,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="82" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="204" applyFont="1"/>
     <xf numFmtId="9" fontId="74" fillId="0" borderId="0" xfId="204" applyFont="1" applyAlignment="1">
@@ -1634,15 +1742,9 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="34" borderId="11" xfId="204" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="35" borderId="0" xfId="204" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="84" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="37" borderId="0" xfId="204" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="36" borderId="0" xfId="204" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="34" borderId="1" xfId="204" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="85" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="38" borderId="1" xfId="204" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="83" fillId="38" borderId="1" xfId="204" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1651,6 +1753,7 @@
     <xf numFmtId="9" fontId="0" fillId="39" borderId="1" xfId="204" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="53" fillId="33" borderId="1" xfId="204" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="53" fillId="40" borderId="0" xfId="204" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="205">
     <cellStyle name="20% - Accent1" xfId="41" builtinId="30" customBuiltin="1"/>
@@ -2166,7 +2269,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{669DF689-B0D6-46EA-ACFD-66E425F22CA2}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AG52"/>
+  <dimension ref="A1:AG90"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="7.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -2287,8 +2390,8 @@
       <c r="AA1" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="AB1" s="18" t="s">
-        <v>127</v>
+      <c r="AB1" s="16" t="s">
+        <v>126</v>
       </c>
       <c r="AC1" s="5" t="s">
         <v>39</v>
@@ -2320,7 +2423,7 @@
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
-      <c r="J2" s="9" t="s">
+      <c r="J2" s="18" t="s">
         <v>98</v>
       </c>
       <c r="K2" s="1"/>
@@ -2330,7 +2433,7 @@
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
-      <c r="R2" s="10" t="s">
+      <c r="R2" s="9" t="s">
         <v>69</v>
       </c>
       <c r="S2" s="1"/>
@@ -2338,14 +2441,14 @@
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
       <c r="W2" s="1"/>
-      <c r="X2" s="11" t="s">
+      <c r="X2" s="10" t="s">
         <v>73</v>
       </c>
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
       <c r="AA2" s="1"/>
-      <c r="AB2" s="19" t="s">
-        <v>128</v>
+      <c r="AB2" s="17" t="s">
+        <v>127</v>
       </c>
       <c r="AC2" s="1"/>
       <c r="AD2" s="1"/>
@@ -2354,10 +2457,10 @@
       <c r="AG2" s="3"/>
     </row>
     <row r="3" spans="1:33">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="11" t="s">
         <v>15</v>
       </c>
       <c r="C3" s="8" t="s">
@@ -2369,7 +2472,7 @@
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
-      <c r="J3" s="13" t="s">
+      <c r="J3" s="18" t="s">
         <v>95</v>
       </c>
       <c r="K3" s="1"/>
@@ -2379,7 +2482,7 @@
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
-      <c r="R3" s="10" t="s">
+      <c r="R3" s="9" t="s">
         <v>70</v>
       </c>
       <c r="S3" s="1"/>
@@ -2387,13 +2490,13 @@
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
       <c r="W3" s="1"/>
-      <c r="X3" s="11" t="s">
+      <c r="X3" s="10" t="s">
         <v>74</v>
       </c>
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
       <c r="AA3" s="1"/>
-      <c r="AB3" s="19" t="s">
+      <c r="AB3" s="17" t="s">
         <v>71</v>
       </c>
       <c r="AC3" s="1"/>
@@ -2403,10 +2506,10 @@
       <c r="AG3" s="3"/>
     </row>
     <row r="4" spans="1:33">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="8" t="s">
@@ -2418,7 +2521,7 @@
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
-      <c r="J4" s="13" t="s">
+      <c r="J4" s="18" t="s">
         <v>99</v>
       </c>
       <c r="K4" s="1"/>
@@ -2434,13 +2537,13 @@
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
       <c r="W4" s="1"/>
-      <c r="X4" s="11" t="s">
+      <c r="X4" s="10" t="s">
         <v>75</v>
       </c>
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
       <c r="AA4" s="1"/>
-      <c r="AB4" s="19" t="s">
+      <c r="AB4" s="17" t="s">
         <v>72</v>
       </c>
       <c r="AC4" s="1"/>
@@ -2450,10 +2553,10 @@
       <c r="AG4" s="3"/>
     </row>
     <row r="5" spans="1:33">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="11" t="s">
         <v>17</v>
       </c>
       <c r="C5" s="8" t="s">
@@ -2465,7 +2568,7 @@
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
-      <c r="J5" s="13" t="s">
+      <c r="J5" s="18" t="s">
         <v>100</v>
       </c>
       <c r="K5" s="1"/>
@@ -2493,10 +2596,10 @@
       <c r="AG5" s="3"/>
     </row>
     <row r="6" spans="1:33">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="11" t="s">
         <v>18</v>
       </c>
       <c r="C6" s="1"/>
@@ -2506,7 +2609,7 @@
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
-      <c r="J6" s="13" t="s">
+      <c r="J6" s="18" t="s">
         <v>91</v>
       </c>
       <c r="K6" s="1"/>
@@ -2534,10 +2637,10 @@
       <c r="AG6" s="3"/>
     </row>
     <row r="7" spans="1:33">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="11" t="s">
         <v>19</v>
       </c>
       <c r="C7" s="1"/>
@@ -2547,7 +2650,7 @@
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
-      <c r="J7" s="13" t="s">
+      <c r="J7" s="18" t="s">
         <v>81</v>
       </c>
       <c r="K7" s="1"/>
@@ -2575,10 +2678,10 @@
       <c r="AG7" s="3"/>
     </row>
     <row r="8" spans="1:33">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="11" t="s">
         <v>20</v>
       </c>
       <c r="C8" s="1"/>
@@ -2588,7 +2691,7 @@
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
-      <c r="J8" s="13" t="s">
+      <c r="J8" s="18" t="s">
         <v>76</v>
       </c>
       <c r="K8" s="1"/>
@@ -2616,10 +2719,10 @@
       <c r="AG8" s="3"/>
     </row>
     <row r="9" spans="1:33">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="11" t="s">
         <v>21</v>
       </c>
       <c r="C9" s="1"/>
@@ -2629,7 +2732,7 @@
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
-      <c r="J9" s="13" t="s">
+      <c r="J9" s="18" t="s">
         <v>101</v>
       </c>
       <c r="K9" s="1"/>
@@ -2657,10 +2760,10 @@
       <c r="AG9" s="3"/>
     </row>
     <row r="10" spans="1:33">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="11" t="s">
         <v>22</v>
       </c>
       <c r="C10" s="1"/>
@@ -2670,7 +2773,7 @@
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
-      <c r="J10" s="13" t="s">
+      <c r="J10" s="18" t="s">
         <v>90</v>
       </c>
       <c r="K10" s="1"/>
@@ -2698,10 +2801,10 @@
       <c r="AG10" s="3"/>
     </row>
     <row r="11" spans="1:33">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C11" s="1"/>
@@ -2711,7 +2814,7 @@
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
-      <c r="J11" s="13" t="s">
+      <c r="J11" s="18" t="s">
         <v>88</v>
       </c>
       <c r="K11" s="1"/>
@@ -2748,7 +2851,7 @@
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
-      <c r="J12" s="13" t="s">
+      <c r="J12" s="18" t="s">
         <v>87</v>
       </c>
       <c r="K12" s="1"/>
@@ -2776,211 +2879,211 @@
       <c r="AG12" s="3"/>
     </row>
     <row r="13" spans="1:33">
-      <c r="A13" s="14" t="s">
+      <c r="A13" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="J13" s="13" t="s">
+      <c r="J13" s="18" t="s">
         <v>102</v>
       </c>
       <c r="AG13" s="3"/>
     </row>
     <row r="14" spans="1:33">
-      <c r="A14" s="14" t="s">
+      <c r="A14" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="J14" s="13" t="s">
+      <c r="J14" s="18" t="s">
         <v>84</v>
       </c>
       <c r="AG14" s="3"/>
     </row>
     <row r="15" spans="1:33">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="J15" s="13" t="s">
+      <c r="J15" s="18" t="s">
         <v>97</v>
       </c>
       <c r="AG15" s="3"/>
     </row>
     <row r="16" spans="1:33">
-      <c r="A16" s="14" t="s">
+      <c r="A16" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="J16" s="13" t="s">
+      <c r="J16" s="18" t="s">
         <v>103</v>
       </c>
       <c r="AG16" s="3"/>
     </row>
     <row r="17" spans="1:33">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="J17" s="13" t="s">
+      <c r="J17" s="18" t="s">
         <v>104</v>
       </c>
       <c r="AG17" s="3"/>
     </row>
     <row r="18" spans="1:33">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="J18" s="13" t="s">
+      <c r="J18" s="18" t="s">
         <v>78</v>
       </c>
       <c r="AG18" s="3"/>
     </row>
     <row r="19" spans="1:33">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="J19" s="13" t="s">
+      <c r="J19" s="18" t="s">
         <v>105</v>
       </c>
       <c r="AG19" s="3"/>
     </row>
     <row r="20" spans="1:33">
-      <c r="A20" s="14" t="s">
+      <c r="A20" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="B20" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="J20" s="13" t="s">
+      <c r="J20" s="18" t="s">
         <v>106</v>
       </c>
       <c r="AG20" s="3"/>
     </row>
     <row r="21" spans="1:33">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="B21" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="J21" s="13" t="s">
+      <c r="J21" s="18" t="s">
         <v>107</v>
       </c>
       <c r="AG21" s="3"/>
     </row>
     <row r="22" spans="1:33">
-      <c r="J22" s="13" t="s">
+      <c r="J22" s="18" t="s">
         <v>79</v>
       </c>
       <c r="AG22" s="3"/>
     </row>
     <row r="23" spans="1:33">
-      <c r="A23" s="16" t="s">
+      <c r="A23" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="B23" s="16" t="s">
+      <c r="B23" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="J23" s="13" t="s">
+      <c r="J23" s="18" t="s">
         <v>108</v>
       </c>
       <c r="AG23" s="3"/>
     </row>
     <row r="24" spans="1:33">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="J24" s="13" t="s">
+      <c r="J24" s="18" t="s">
         <v>109</v>
       </c>
       <c r="AG24" s="3"/>
     </row>
     <row r="25" spans="1:33">
-      <c r="A25" s="16" t="s">
+      <c r="A25" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="B25" s="16" t="s">
+      <c r="B25" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="J25" s="13" t="s">
+      <c r="J25" s="18" t="s">
         <v>86</v>
       </c>
       <c r="AG25" s="3"/>
     </row>
     <row r="26" spans="1:33">
-      <c r="A26" s="16" t="s">
+      <c r="A26" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="B26" s="16" t="s">
+      <c r="B26" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="J26" s="13" t="s">
+      <c r="J26" s="18" t="s">
         <v>82</v>
       </c>
       <c r="AG26" s="3"/>
     </row>
     <row r="27" spans="1:33">
-      <c r="A27" s="16" t="s">
+      <c r="A27" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="B27" s="16" t="s">
+      <c r="B27" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="J27" s="13" t="s">
+      <c r="J27" s="18" t="s">
         <v>96</v>
       </c>
       <c r="AG27" s="3"/>
     </row>
     <row r="28" spans="1:33">
-      <c r="A28" s="16" t="s">
+      <c r="A28" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="B28" s="16" t="s">
+      <c r="B28" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="J28" s="13" t="s">
+      <c r="J28" s="18" t="s">
         <v>85</v>
       </c>
       <c r="AG28" s="3"/>
     </row>
     <row r="29" spans="1:33">
-      <c r="A29" s="16" t="s">
+      <c r="A29" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="B29" s="16" t="s">
+      <c r="B29" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="J29" s="13" t="s">
+      <c r="J29" s="18" t="s">
         <v>110</v>
       </c>
       <c r="AG29" s="3"/>
     </row>
     <row r="30" spans="1:33">
-      <c r="A30" s="16" t="s">
+      <c r="A30" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="B30" s="16" t="s">
+      <c r="B30" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="J30" s="13" t="s">
+      <c r="J30" s="18" t="s">
         <v>77</v>
       </c>
       <c r="AG30" s="3"/>
@@ -2988,178 +3091,368 @@
     <row r="31" spans="1:33">
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
-      <c r="J31" s="13" t="s">
+      <c r="J31" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="AG31" s="3"/>
+    </row>
+    <row r="32" spans="1:33">
+      <c r="A32" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="J32" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="AG32" s="3"/>
+    </row>
+    <row r="33" spans="1:33">
+      <c r="A33" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="J33" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="AG31" s="3"/>
-    </row>
-    <row r="32" spans="1:33">
-      <c r="A32" s="17" t="s">
+      <c r="AG33" s="3"/>
+    </row>
+    <row r="34" spans="1:33">
+      <c r="A34" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="B32" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="J32" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="AG32" s="3"/>
-    </row>
-    <row r="33" spans="1:33">
-      <c r="A33" s="17" t="s">
+      <c r="B34" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="J34" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="AG34" s="3"/>
+    </row>
+    <row r="35" spans="1:33">
+      <c r="A35" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="B33" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="J33" s="13" t="s">
+      <c r="B35" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="J35" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="AG33" s="3"/>
-    </row>
-    <row r="34" spans="1:33">
-      <c r="A34" s="17" t="s">
+      <c r="AG35" s="3"/>
+    </row>
+    <row r="36" spans="1:33">
+      <c r="A36" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="B34" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="J34" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="AG34" s="3"/>
-    </row>
-    <row r="35" spans="1:33">
-      <c r="A35" s="17" t="s">
+      <c r="B36" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="J36" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="AG36" s="3"/>
+    </row>
+    <row r="37" spans="1:33">
+      <c r="A37" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="B35" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="J35" s="13" t="s">
+      <c r="B37" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="J37" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG37" s="3"/>
+    </row>
+    <row r="38" spans="1:33">
+      <c r="A38" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="B38" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="J38" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="AG38" s="3"/>
+    </row>
+    <row r="39" spans="1:33">
+      <c r="J39" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="AG35" s="3"/>
-    </row>
-    <row r="36" spans="1:33">
-      <c r="A36" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="B36" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="J36" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="AG36" s="3"/>
-    </row>
-    <row r="37" spans="1:33">
-      <c r="A37" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="B37" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="J37" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="AG37" s="3"/>
-    </row>
-    <row r="38" spans="1:33">
-      <c r="A38" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="B38" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="J38" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="AG38" s="3"/>
-    </row>
-    <row r="39" spans="1:33">
-      <c r="J39" s="13" t="s">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="1:33">
+      <c r="J40" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="1:33">
-      <c r="J40" s="13" t="s">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="1:33">
+      <c r="J41" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="AG41" s="3"/>
+    </row>
+    <row r="42" spans="1:33">
+      <c r="J42" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="1:33">
-      <c r="J41" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="AG41" s="3"/>
-    </row>
-    <row r="42" spans="1:33">
-      <c r="J42" s="13" t="s">
+      <c r="AG42" s="3"/>
+    </row>
+    <row r="43" spans="1:33">
+      <c r="J43" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="AG42" s="3"/>
-    </row>
-    <row r="43" spans="1:33">
-      <c r="J43" s="13" t="s">
+      <c r="AG43" s="3"/>
+    </row>
+    <row r="44" spans="1:33">
+      <c r="J44" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="AG43" s="3"/>
-    </row>
-    <row r="44" spans="1:33">
-      <c r="J44" s="13" t="s">
+      <c r="AG44" s="3"/>
+    </row>
+    <row r="45" spans="1:33">
+      <c r="J45" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="AG44" s="3"/>
-    </row>
-    <row r="45" spans="1:33">
-      <c r="J45" s="13" t="s">
+      <c r="AG45" s="3"/>
+    </row>
+    <row r="46" spans="1:33">
+      <c r="J46" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="AG45" s="3"/>
-    </row>
-    <row r="46" spans="1:33">
-      <c r="J46" s="13" t="s">
+      <c r="AG46" s="3"/>
+    </row>
+    <row r="47" spans="1:33">
+      <c r="J47" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="AG46" s="3"/>
-    </row>
-    <row r="47" spans="1:33">
-      <c r="J47" s="13" t="s">
+      <c r="AG47" s="3"/>
+    </row>
+    <row r="48" spans="1:33">
+      <c r="J48" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="AG47" s="3"/>
-    </row>
-    <row r="48" spans="1:33">
-      <c r="J48" s="13" t="s">
+      <c r="AG48" s="3"/>
+    </row>
+    <row r="49" spans="10:33">
+      <c r="J49" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="AG48" s="3"/>
-    </row>
-    <row r="49" spans="10:33">
-      <c r="J49" s="13" t="s">
+      <c r="AG49" s="3"/>
+    </row>
+    <row r="50" spans="10:33">
+      <c r="J50" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="AG49" s="3"/>
-    </row>
-    <row r="50" spans="10:33">
-      <c r="J50" s="13" t="s">
+      <c r="AG50" s="3"/>
+    </row>
+    <row r="51" spans="10:33">
+      <c r="J51" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="AG50" s="3"/>
-    </row>
-    <row r="51" spans="10:33">
-      <c r="J51" s="13" t="s">
+      <c r="AG51" s="3"/>
+    </row>
+    <row r="52" spans="10:33">
+      <c r="J52" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="AG51" s="3"/>
-    </row>
-    <row r="52" spans="10:33">
-      <c r="J52" s="13" t="s">
-        <v>126</v>
-      </c>
       <c r="AG52" s="3"/>
+    </row>
+    <row r="53" spans="10:33">
+      <c r="J53" s="18" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="54" spans="10:33">
+      <c r="J54" s="18" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="55" spans="10:33">
+      <c r="J55" s="18" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="56" spans="10:33">
+      <c r="J56" s="18" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="57" spans="10:33">
+      <c r="J57" s="18" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="58" spans="10:33">
+      <c r="J58" s="18" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="59" spans="10:33">
+      <c r="J59" s="18" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="60" spans="10:33">
+      <c r="J60" s="18" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="61" spans="10:33">
+      <c r="J61" s="18" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="62" spans="10:33">
+      <c r="J62" s="18" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="63" spans="10:33">
+      <c r="J63" s="18" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="64" spans="10:33">
+      <c r="J64" s="18" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="65" spans="10:10">
+      <c r="J65" s="18" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="66" spans="10:10">
+      <c r="J66" s="18" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="67" spans="10:10">
+      <c r="J67" s="18" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="68" spans="10:10">
+      <c r="J68" s="18" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="69" spans="10:10">
+      <c r="J69" s="18" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="70" spans="10:10">
+      <c r="J70" s="18" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="71" spans="10:10">
+      <c r="J71" s="18" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="72" spans="10:10">
+      <c r="J72" s="18" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="73" spans="10:10">
+      <c r="J73" s="18" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="74" spans="10:10">
+      <c r="J74" s="18" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="75" spans="10:10">
+      <c r="J75" s="18" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="76" spans="10:10">
+      <c r="J76" s="18" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="77" spans="10:10">
+      <c r="J77" s="18" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="78" spans="10:10">
+      <c r="J78" s="18" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="79" spans="10:10">
+      <c r="J79" s="18" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="80" spans="10:10">
+      <c r="J80" s="18" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="81" spans="10:10">
+      <c r="J81" s="18" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="82" spans="10:10">
+      <c r="J82" s="18" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="83" spans="10:10">
+      <c r="J83" s="18" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="84" spans="10:10">
+      <c r="J84" s="18" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="85" spans="10:10">
+      <c r="J85" s="18" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="86" spans="10:10">
+      <c r="J86" s="18" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="87" spans="10:10">
+      <c r="J87" s="18" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="88" spans="10:10">
+      <c r="J88" s="18" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="89" spans="10:10">
+      <c r="J89" s="18" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="90" spans="10:10">
+      <c r="J90" s="18" t="s">
+        <v>166</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="81" type="noConversion"/>

--- a/frontend/public/formats/physical_format.xlsx
+++ b/frontend/public/formats/physical_format.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PROJECTS FOLDER\SG ENCON\frontend\public\formats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63097CD8-1954-4524-AAAE-83631F32431B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E849F1E-61A5-4E50-AE25-A2D173F519A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="168">
   <si>
     <t>Cluster</t>
   </si>
@@ -549,6 +549,9 @@
   </si>
   <si>
     <t>Zonal Fiber SME</t>
+  </si>
+  <si>
+    <t>NTH Salary</t>
   </si>
 </sst>
 </file>
@@ -559,7 +562,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;₹&quot;\ * #,##0.00_ ;_ &quot;₹&quot;\ * \-#,##0.00_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="84">
+  <fonts count="85">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1139,8 +1142,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="42">
+  <fills count="43">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1371,6 +1380,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1726,7 +1741,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="82" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="204" applyFont="1"/>
     <xf numFmtId="9" fontId="74" fillId="0" borderId="0" xfId="204" applyFont="1" applyAlignment="1">
@@ -1737,9 +1752,6 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="204" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="33" borderId="1" xfId="204" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="33" borderId="1" xfId="204" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="34" borderId="11" xfId="204" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="35" borderId="0" xfId="204" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="37" borderId="0" xfId="204" applyFont="1" applyFill="1"/>
@@ -1751,9 +1763,17 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="35" borderId="1" xfId="204" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="39" borderId="1" xfId="204" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="53" fillId="33" borderId="1" xfId="204" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="53" fillId="40" borderId="0" xfId="204" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="41" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="9" fontId="74" fillId="33" borderId="0" xfId="204" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="84" fillId="42" borderId="1" xfId="204" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="42" borderId="1" xfId="204" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="42" borderId="1" xfId="204" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="53" fillId="42" borderId="1" xfId="204" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="205">
     <cellStyle name="20% - Accent1" xfId="41" builtinId="30" customBuiltin="1"/>
@@ -2309,13 +2329,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="18" t="s">
         <v>8</v>
       </c>
       <c r="D1" s="5" t="s">
@@ -2336,7 +2356,7 @@
       <c r="I1" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="20" t="s">
         <v>3</v>
       </c>
       <c r="K1" s="5" t="s">
@@ -2360,7 +2380,7 @@
       <c r="Q1" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="R1" s="19" t="s">
         <v>13</v>
       </c>
       <c r="S1" s="5" t="s">
@@ -2378,7 +2398,7 @@
       <c r="W1" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="X1" s="5" t="s">
+      <c r="X1" s="19" t="s">
         <v>7</v>
       </c>
       <c r="Y1" s="5" t="s">
@@ -2390,7 +2410,7 @@
       <c r="AA1" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="AB1" s="16" t="s">
+      <c r="AB1" s="21" t="s">
         <v>126</v>
       </c>
       <c r="AC1" s="5" t="s">
@@ -2405,16 +2425,18 @@
       <c r="AF1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="AG1" s="3"/>
+      <c r="AG1" s="17" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="2" spans="1:33">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="7" t="s">
         <v>69</v>
       </c>
       <c r="D2" s="1"/>
@@ -2423,7 +2445,7 @@
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
-      <c r="J2" s="18" t="s">
+      <c r="J2" s="16" t="s">
         <v>98</v>
       </c>
       <c r="K2" s="1"/>
@@ -2433,7 +2455,7 @@
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
-      <c r="R2" s="9" t="s">
+      <c r="R2" s="8" t="s">
         <v>69</v>
       </c>
       <c r="S2" s="1"/>
@@ -2441,13 +2463,13 @@
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
       <c r="W2" s="1"/>
-      <c r="X2" s="10" t="s">
+      <c r="X2" s="9" t="s">
         <v>73</v>
       </c>
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
       <c r="AA2" s="1"/>
-      <c r="AB2" s="17" t="s">
+      <c r="AB2" s="15" t="s">
         <v>127</v>
       </c>
       <c r="AC2" s="1"/>
@@ -2457,13 +2479,13 @@
       <c r="AG2" s="3"/>
     </row>
     <row r="3" spans="1:33">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="7" t="s">
         <v>70</v>
       </c>
       <c r="D3" s="1"/>
@@ -2472,7 +2494,7 @@
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
-      <c r="J3" s="18" t="s">
+      <c r="J3" s="16" t="s">
         <v>95</v>
       </c>
       <c r="K3" s="1"/>
@@ -2482,7 +2504,7 @@
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
-      <c r="R3" s="9" t="s">
+      <c r="R3" s="8" t="s">
         <v>70</v>
       </c>
       <c r="S3" s="1"/>
@@ -2490,13 +2512,13 @@
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
       <c r="W3" s="1"/>
-      <c r="X3" s="10" t="s">
+      <c r="X3" s="9" t="s">
         <v>74</v>
       </c>
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
       <c r="AA3" s="1"/>
-      <c r="AB3" s="17" t="s">
+      <c r="AB3" s="15" t="s">
         <v>71</v>
       </c>
       <c r="AC3" s="1"/>
@@ -2506,13 +2528,13 @@
       <c r="AG3" s="3"/>
     </row>
     <row r="4" spans="1:33">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>71</v>
       </c>
       <c r="D4" s="1"/>
@@ -2521,7 +2543,7 @@
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
-      <c r="J4" s="18" t="s">
+      <c r="J4" s="16" t="s">
         <v>99</v>
       </c>
       <c r="K4" s="1"/>
@@ -2537,13 +2559,13 @@
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
       <c r="W4" s="1"/>
-      <c r="X4" s="10" t="s">
+      <c r="X4" s="9" t="s">
         <v>75</v>
       </c>
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
       <c r="AA4" s="1"/>
-      <c r="AB4" s="17" t="s">
+      <c r="AB4" s="15" t="s">
         <v>72</v>
       </c>
       <c r="AC4" s="1"/>
@@ -2553,13 +2575,13 @@
       <c r="AG4" s="3"/>
     </row>
     <row r="5" spans="1:33">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>72</v>
       </c>
       <c r="D5" s="1"/>
@@ -2568,7 +2590,7 @@
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
-      <c r="J5" s="18" t="s">
+      <c r="J5" s="16" t="s">
         <v>100</v>
       </c>
       <c r="K5" s="1"/>
@@ -2596,10 +2618,10 @@
       <c r="AG5" s="3"/>
     </row>
     <row r="6" spans="1:33">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="10" t="s">
         <v>18</v>
       </c>
       <c r="C6" s="1"/>
@@ -2609,7 +2631,7 @@
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
-      <c r="J6" s="18" t="s">
+      <c r="J6" s="16" t="s">
         <v>91</v>
       </c>
       <c r="K6" s="1"/>
@@ -2637,10 +2659,10 @@
       <c r="AG6" s="3"/>
     </row>
     <row r="7" spans="1:33">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="10" t="s">
         <v>19</v>
       </c>
       <c r="C7" s="1"/>
@@ -2650,7 +2672,7 @@
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
-      <c r="J7" s="18" t="s">
+      <c r="J7" s="16" t="s">
         <v>81</v>
       </c>
       <c r="K7" s="1"/>
@@ -2678,10 +2700,10 @@
       <c r="AG7" s="3"/>
     </row>
     <row r="8" spans="1:33">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="10" t="s">
         <v>20</v>
       </c>
       <c r="C8" s="1"/>
@@ -2691,7 +2713,7 @@
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
-      <c r="J8" s="18" t="s">
+      <c r="J8" s="16" t="s">
         <v>76</v>
       </c>
       <c r="K8" s="1"/>
@@ -2719,10 +2741,10 @@
       <c r="AG8" s="3"/>
     </row>
     <row r="9" spans="1:33">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="10" t="s">
         <v>21</v>
       </c>
       <c r="C9" s="1"/>
@@ -2732,7 +2754,7 @@
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
-      <c r="J9" s="18" t="s">
+      <c r="J9" s="16" t="s">
         <v>101</v>
       </c>
       <c r="K9" s="1"/>
@@ -2760,10 +2782,10 @@
       <c r="AG9" s="3"/>
     </row>
     <row r="10" spans="1:33">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="10" t="s">
         <v>22</v>
       </c>
       <c r="C10" s="1"/>
@@ -2773,7 +2795,7 @@
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
-      <c r="J10" s="18" t="s">
+      <c r="J10" s="16" t="s">
         <v>90</v>
       </c>
       <c r="K10" s="1"/>
@@ -2801,10 +2823,10 @@
       <c r="AG10" s="3"/>
     </row>
     <row r="11" spans="1:33">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="10" t="s">
         <v>23</v>
       </c>
       <c r="C11" s="1"/>
@@ -2814,7 +2836,7 @@
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
-      <c r="J11" s="18" t="s">
+      <c r="J11" s="16" t="s">
         <v>88</v>
       </c>
       <c r="K11" s="1"/>
@@ -2851,7 +2873,7 @@
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
-      <c r="J12" s="18" t="s">
+      <c r="J12" s="16" t="s">
         <v>87</v>
       </c>
       <c r="K12" s="1"/>
@@ -2879,211 +2901,211 @@
       <c r="AG12" s="3"/>
     </row>
     <row r="13" spans="1:33">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="J13" s="18" t="s">
+      <c r="J13" s="16" t="s">
         <v>102</v>
       </c>
       <c r="AG13" s="3"/>
     </row>
     <row r="14" spans="1:33">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="J14" s="18" t="s">
+      <c r="J14" s="16" t="s">
         <v>84</v>
       </c>
       <c r="AG14" s="3"/>
     </row>
     <row r="15" spans="1:33">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="J15" s="18" t="s">
+      <c r="J15" s="16" t="s">
         <v>97</v>
       </c>
       <c r="AG15" s="3"/>
     </row>
     <row r="16" spans="1:33">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="J16" s="18" t="s">
+      <c r="J16" s="16" t="s">
         <v>103</v>
       </c>
       <c r="AG16" s="3"/>
     </row>
     <row r="17" spans="1:33">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="J17" s="18" t="s">
+      <c r="J17" s="16" t="s">
         <v>104</v>
       </c>
       <c r="AG17" s="3"/>
     </row>
     <row r="18" spans="1:33">
-      <c r="A18" s="12" t="s">
+      <c r="A18" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="J18" s="18" t="s">
+      <c r="J18" s="16" t="s">
         <v>78</v>
       </c>
       <c r="AG18" s="3"/>
     </row>
     <row r="19" spans="1:33">
-      <c r="A19" s="12" t="s">
+      <c r="A19" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="B19" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="J19" s="18" t="s">
+      <c r="J19" s="16" t="s">
         <v>105</v>
       </c>
       <c r="AG19" s="3"/>
     </row>
     <row r="20" spans="1:33">
-      <c r="A20" s="12" t="s">
+      <c r="A20" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="J20" s="18" t="s">
+      <c r="J20" s="16" t="s">
         <v>106</v>
       </c>
       <c r="AG20" s="3"/>
     </row>
     <row r="21" spans="1:33">
-      <c r="A21" s="12" t="s">
+      <c r="A21" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="13" t="s">
+      <c r="B21" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="J21" s="18" t="s">
+      <c r="J21" s="16" t="s">
         <v>107</v>
       </c>
       <c r="AG21" s="3"/>
     </row>
     <row r="22" spans="1:33">
-      <c r="J22" s="18" t="s">
+      <c r="J22" s="16" t="s">
         <v>79</v>
       </c>
       <c r="AG22" s="3"/>
     </row>
     <row r="23" spans="1:33">
-      <c r="A23" s="14" t="s">
+      <c r="A23" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="B23" s="14" t="s">
+      <c r="B23" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="J23" s="18" t="s">
+      <c r="J23" s="16" t="s">
         <v>108</v>
       </c>
       <c r="AG23" s="3"/>
     </row>
     <row r="24" spans="1:33">
-      <c r="A24" s="14" t="s">
+      <c r="A24" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="B24" s="14" t="s">
+      <c r="B24" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="J24" s="18" t="s">
+      <c r="J24" s="16" t="s">
         <v>109</v>
       </c>
       <c r="AG24" s="3"/>
     </row>
     <row r="25" spans="1:33">
-      <c r="A25" s="14" t="s">
+      <c r="A25" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="B25" s="14" t="s">
+      <c r="B25" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="J25" s="18" t="s">
+      <c r="J25" s="16" t="s">
         <v>86</v>
       </c>
       <c r="AG25" s="3"/>
     </row>
     <row r="26" spans="1:33">
-      <c r="A26" s="14" t="s">
+      <c r="A26" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="B26" s="14" t="s">
+      <c r="B26" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="J26" s="18" t="s">
+      <c r="J26" s="16" t="s">
         <v>82</v>
       </c>
       <c r="AG26" s="3"/>
     </row>
     <row r="27" spans="1:33">
-      <c r="A27" s="14" t="s">
+      <c r="A27" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="B27" s="14" t="s">
+      <c r="B27" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="J27" s="18" t="s">
+      <c r="J27" s="16" t="s">
         <v>96</v>
       </c>
       <c r="AG27" s="3"/>
     </row>
     <row r="28" spans="1:33">
-      <c r="A28" s="14" t="s">
+      <c r="A28" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="B28" s="14" t="s">
+      <c r="B28" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="J28" s="18" t="s">
+      <c r="J28" s="16" t="s">
         <v>85</v>
       </c>
       <c r="AG28" s="3"/>
     </row>
     <row r="29" spans="1:33">
-      <c r="A29" s="14" t="s">
+      <c r="A29" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="B29" s="14" t="s">
+      <c r="B29" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="J29" s="18" t="s">
+      <c r="J29" s="16" t="s">
         <v>110</v>
       </c>
       <c r="AG29" s="3"/>
     </row>
     <row r="30" spans="1:33">
-      <c r="A30" s="14" t="s">
+      <c r="A30" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="B30" s="14" t="s">
+      <c r="B30" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="J30" s="18" t="s">
+      <c r="J30" s="16" t="s">
         <v>77</v>
       </c>
       <c r="AG30" s="3"/>
@@ -3091,366 +3113,366 @@
     <row r="31" spans="1:33">
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
-      <c r="J31" s="18" t="s">
+      <c r="J31" s="16" t="s">
         <v>128</v>
       </c>
       <c r="AG31" s="3"/>
     </row>
     <row r="32" spans="1:33">
-      <c r="A32" s="15" t="s">
+      <c r="A32" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="B32" s="15" t="s">
+      <c r="B32" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="J32" s="18" t="s">
+      <c r="J32" s="16" t="s">
         <v>89</v>
       </c>
       <c r="AG32" s="3"/>
     </row>
     <row r="33" spans="1:33">
-      <c r="A33" s="15" t="s">
+      <c r="A33" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="B33" s="15" t="s">
+      <c r="B33" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="J33" s="18" t="s">
+      <c r="J33" s="16" t="s">
         <v>111</v>
       </c>
       <c r="AG33" s="3"/>
     </row>
     <row r="34" spans="1:33">
-      <c r="A34" s="15" t="s">
+      <c r="A34" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="J34" s="18" t="s">
+      <c r="J34" s="16" t="s">
         <v>93</v>
       </c>
       <c r="AG34" s="3"/>
     </row>
     <row r="35" spans="1:33">
-      <c r="A35" s="15" t="s">
+      <c r="A35" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="B35" s="15" t="s">
+      <c r="B35" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="J35" s="18" t="s">
+      <c r="J35" s="16" t="s">
         <v>112</v>
       </c>
       <c r="AG35" s="3"/>
     </row>
     <row r="36" spans="1:33">
-      <c r="A36" s="15" t="s">
+      <c r="A36" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="15" t="s">
+      <c r="B36" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="J36" s="18" t="s">
+      <c r="J36" s="16" t="s">
         <v>80</v>
       </c>
       <c r="AG36" s="3"/>
     </row>
     <row r="37" spans="1:33">
-      <c r="A37" s="15" t="s">
+      <c r="A37" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="B37" s="15" t="s">
+      <c r="B37" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="J37" s="18" t="s">
+      <c r="J37" s="16" t="s">
         <v>83</v>
       </c>
       <c r="AG37" s="3"/>
     </row>
     <row r="38" spans="1:33">
-      <c r="A38" s="15" t="s">
+      <c r="A38" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="B38" s="15" t="s">
+      <c r="B38" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="J38" s="18" t="s">
+      <c r="J38" s="16" t="s">
         <v>94</v>
       </c>
       <c r="AG38" s="3"/>
     </row>
     <row r="39" spans="1:33">
-      <c r="J39" s="18" t="s">
+      <c r="J39" s="16" t="s">
         <v>113</v>
       </c>
       <c r="AG39" s="3"/>
     </row>
     <row r="40" spans="1:33">
-      <c r="J40" s="18" t="s">
+      <c r="J40" s="16" t="s">
         <v>114</v>
       </c>
       <c r="AG40" s="3"/>
     </row>
     <row r="41" spans="1:33">
-      <c r="J41" s="18" t="s">
+      <c r="J41" s="16" t="s">
         <v>92</v>
       </c>
       <c r="AG41" s="3"/>
     </row>
     <row r="42" spans="1:33">
-      <c r="J42" s="18" t="s">
+      <c r="J42" s="16" t="s">
         <v>115</v>
       </c>
       <c r="AG42" s="3"/>
     </row>
     <row r="43" spans="1:33">
-      <c r="J43" s="18" t="s">
+      <c r="J43" s="16" t="s">
         <v>116</v>
       </c>
       <c r="AG43" s="3"/>
     </row>
     <row r="44" spans="1:33">
-      <c r="J44" s="18" t="s">
+      <c r="J44" s="16" t="s">
         <v>117</v>
       </c>
       <c r="AG44" s="3"/>
     </row>
     <row r="45" spans="1:33">
-      <c r="J45" s="18" t="s">
+      <c r="J45" s="16" t="s">
         <v>118</v>
       </c>
       <c r="AG45" s="3"/>
     </row>
     <row r="46" spans="1:33">
-      <c r="J46" s="18" t="s">
+      <c r="J46" s="16" t="s">
         <v>119</v>
       </c>
       <c r="AG46" s="3"/>
     </row>
     <row r="47" spans="1:33">
-      <c r="J47" s="18" t="s">
+      <c r="J47" s="16" t="s">
         <v>120</v>
       </c>
       <c r="AG47" s="3"/>
     </row>
     <row r="48" spans="1:33">
-      <c r="J48" s="18" t="s">
+      <c r="J48" s="16" t="s">
         <v>121</v>
       </c>
       <c r="AG48" s="3"/>
     </row>
     <row r="49" spans="10:33">
-      <c r="J49" s="18" t="s">
+      <c r="J49" s="16" t="s">
         <v>122</v>
       </c>
       <c r="AG49" s="3"/>
     </row>
     <row r="50" spans="10:33">
-      <c r="J50" s="18" t="s">
+      <c r="J50" s="16" t="s">
         <v>123</v>
       </c>
       <c r="AG50" s="3"/>
     </row>
     <row r="51" spans="10:33">
-      <c r="J51" s="18" t="s">
+      <c r="J51" s="16" t="s">
         <v>124</v>
       </c>
       <c r="AG51" s="3"/>
     </row>
     <row r="52" spans="10:33">
-      <c r="J52" s="18" t="s">
+      <c r="J52" s="16" t="s">
         <v>125</v>
       </c>
       <c r="AG52" s="3"/>
     </row>
     <row r="53" spans="10:33">
-      <c r="J53" s="18" t="s">
+      <c r="J53" s="16" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="54" spans="10:33">
-      <c r="J54" s="18" t="s">
+      <c r="J54" s="16" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="55" spans="10:33">
-      <c r="J55" s="18" t="s">
+      <c r="J55" s="16" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="56" spans="10:33">
-      <c r="J56" s="18" t="s">
+      <c r="J56" s="16" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="57" spans="10:33">
-      <c r="J57" s="18" t="s">
+      <c r="J57" s="16" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="58" spans="10:33">
-      <c r="J58" s="18" t="s">
+      <c r="J58" s="16" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="59" spans="10:33">
-      <c r="J59" s="18" t="s">
+      <c r="J59" s="16" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="60" spans="10:33">
-      <c r="J60" s="18" t="s">
+      <c r="J60" s="16" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="61" spans="10:33">
-      <c r="J61" s="18" t="s">
+      <c r="J61" s="16" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="62" spans="10:33">
-      <c r="J62" s="18" t="s">
+      <c r="J62" s="16" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="63" spans="10:33">
-      <c r="J63" s="18" t="s">
+      <c r="J63" s="16" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="64" spans="10:33">
-      <c r="J64" s="18" t="s">
+      <c r="J64" s="16" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="65" spans="10:10">
-      <c r="J65" s="18" t="s">
+      <c r="J65" s="16" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="66" spans="10:10">
-      <c r="J66" s="18" t="s">
+      <c r="J66" s="16" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="67" spans="10:10">
-      <c r="J67" s="18" t="s">
+      <c r="J67" s="16" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="68" spans="10:10">
-      <c r="J68" s="18" t="s">
+      <c r="J68" s="16" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="69" spans="10:10">
-      <c r="J69" s="18" t="s">
+      <c r="J69" s="16" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="70" spans="10:10">
-      <c r="J70" s="18" t="s">
+      <c r="J70" s="16" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="71" spans="10:10">
-      <c r="J71" s="18" t="s">
+      <c r="J71" s="16" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="72" spans="10:10">
-      <c r="J72" s="18" t="s">
+      <c r="J72" s="16" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="73" spans="10:10">
-      <c r="J73" s="18" t="s">
+      <c r="J73" s="16" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="74" spans="10:10">
-      <c r="J74" s="18" t="s">
+      <c r="J74" s="16" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="75" spans="10:10">
-      <c r="J75" s="18" t="s">
+      <c r="J75" s="16" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="76" spans="10:10">
-      <c r="J76" s="18" t="s">
+      <c r="J76" s="16" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="77" spans="10:10">
-      <c r="J77" s="18" t="s">
+      <c r="J77" s="16" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="78" spans="10:10">
-      <c r="J78" s="18" t="s">
+      <c r="J78" s="16" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="79" spans="10:10">
-      <c r="J79" s="18" t="s">
+      <c r="J79" s="16" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="80" spans="10:10">
-      <c r="J80" s="18" t="s">
+      <c r="J80" s="16" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="81" spans="10:10">
-      <c r="J81" s="18" t="s">
+      <c r="J81" s="16" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="82" spans="10:10">
-      <c r="J82" s="18" t="s">
+      <c r="J82" s="16" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="83" spans="10:10">
-      <c r="J83" s="18" t="s">
+      <c r="J83" s="16" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="84" spans="10:10">
-      <c r="J84" s="18" t="s">
+      <c r="J84" s="16" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="85" spans="10:10">
-      <c r="J85" s="18" t="s">
+      <c r="J85" s="16" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="86" spans="10:10">
-      <c r="J86" s="18" t="s">
+      <c r="J86" s="16" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="87" spans="10:10">
-      <c r="J87" s="18" t="s">
+      <c r="J87" s="16" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="88" spans="10:10">
-      <c r="J88" s="18" t="s">
+      <c r="J88" s="16" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="89" spans="10:10">
-      <c r="J89" s="18" t="s">
+      <c r="J89" s="16" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="90" spans="10:10">
-      <c r="J90" s="18" t="s">
+      <c r="J90" s="16" t="s">
         <v>166</v>
       </c>
     </row>
